--- a/data/output/calendario.xlsx
+++ b/data/output/calendario.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG138"/>
+  <dimension ref="A1:AG111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -546,7 +546,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cobertura 1453/1561 (93.1%)  |  sin cubrir 108  |  P1 138  |  P2 77  |  FEASIBLE</t>
+          <t>Cobertura 1496/1561 (95.8%)  |  sin cubrir 65  |  P1 91  |  P2 68  |  FEASIBLE</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
           <t>correturno</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>VADN010</t>
-        </is>
-      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>VADN038</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="9" t="inlineStr"/>
       <c r="F5" s="9" t="inlineStr"/>
       <c r="G5" s="8" t="inlineStr">
@@ -806,63 +806,63 @@
       </c>
       <c r="P5" s="8" t="inlineStr">
         <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
           <t>VADN012</t>
         </is>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
-        <is>
-          <t>VADN012</t>
-        </is>
-      </c>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t>VADN176</t>
-        </is>
-      </c>
+      <c r="R5" s="8" t="inlineStr"/>
       <c r="S5" s="9" t="inlineStr"/>
-      <c r="T5" s="9" t="inlineStr"/>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>VADN012</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>VADN177</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr"/>
+      <c r="V5" s="8" t="inlineStr"/>
+      <c r="W5" s="8" t="inlineStr">
         <is>
           <t>VADN001</t>
         </is>
       </c>
-      <c r="W5" s="8" t="inlineStr">
+      <c r="X5" s="8" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="Y5" s="8" t="inlineStr">
         <is>
           <t>VADN001</t>
         </is>
       </c>
-      <c r="X5" s="8" t="inlineStr">
-        <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="Y5" s="8" t="inlineStr">
-        <is>
-          <t>VADN176</t>
-        </is>
-      </c>
-      <c r="Z5" s="9" t="inlineStr"/>
+      <c r="Z5" s="9" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
       <c r="AA5" s="9" t="inlineStr"/>
       <c r="AB5" s="8" t="inlineStr">
         <is>
+          <t>VADN176</t>
+        </is>
+      </c>
+      <c r="AC5" s="8" t="inlineStr"/>
+      <c r="AD5" s="8" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="AE5" s="8" t="inlineStr">
+        <is>
           <t>VADN022</t>
         </is>
       </c>
-      <c r="AC5" s="8" t="inlineStr">
-        <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="AD5" s="8" t="inlineStr"/>
-      <c r="AE5" s="8" t="inlineStr"/>
       <c r="AF5" s="8" t="inlineStr">
         <is>
-          <t>VADN033</t>
+          <t>VADP003</t>
         </is>
       </c>
       <c r="AG5" s="9" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>VADN034</t>
+          <t>VADU47127</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr"/>
@@ -985,32 +985,36 @@
           <t>VADN013</t>
         </is>
       </c>
-      <c r="Z6" s="9" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
+      <c r="Z6" s="9" t="inlineStr"/>
       <c r="AA6" s="9" t="inlineStr"/>
-      <c r="AB6" s="8" t="inlineStr"/>
-      <c r="AC6" s="8" t="inlineStr"/>
+      <c r="AB6" s="8" t="inlineStr">
+        <is>
+          <t>VADN013</t>
+        </is>
+      </c>
+      <c r="AC6" s="8" t="inlineStr">
+        <is>
+          <t>VADN013</t>
+        </is>
+      </c>
       <c r="AD6" s="8" t="inlineStr">
         <is>
-          <t>VADN035</t>
+          <t>VADN013</t>
         </is>
       </c>
       <c r="AE6" s="8" t="inlineStr">
         <is>
-          <t>VADN035</t>
+          <t>VADN013</t>
         </is>
       </c>
       <c r="AF6" s="8" t="inlineStr">
         <is>
-          <t>VADN178</t>
+          <t>VADN013</t>
         </is>
       </c>
       <c r="AG6" s="9" t="inlineStr">
         <is>
-          <t>VADN026</t>
+          <t>VADN002</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1035,11 @@
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
       <c r="F7" s="9" t="inlineStr"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
@@ -1041,7 +1049,7 @@
       <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>VADN171</t>
+          <t>VADN040</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -1160,16 +1168,8 @@
           <t>correturno</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>VADN004</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr"/>
       <c r="E8" s="9" t="inlineStr"/>
       <c r="F8" s="9" t="inlineStr"/>
       <c r="G8" s="8" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>VADN029</t>
+          <t>VADN007</t>
         </is>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
-          <t>VADN029</t>
+          <t>VADN007</t>
         </is>
       </c>
       <c r="L8" s="9" t="inlineStr"/>
@@ -1214,12 +1214,12 @@
           <t>VADN051</t>
         </is>
       </c>
-      <c r="Q8" s="8" t="inlineStr"/>
-      <c r="R8" s="8" t="inlineStr">
+      <c r="Q8" s="8" t="inlineStr">
         <is>
           <t>VADN051</t>
         </is>
       </c>
+      <c r="R8" s="8" t="inlineStr"/>
       <c r="S8" s="9" t="inlineStr"/>
       <c r="T8" s="9" t="inlineStr"/>
       <c r="U8" s="8" t="inlineStr">
@@ -1227,50 +1227,50 @@
           <t>VADN172</t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr"/>
-      <c r="W8" s="8" t="inlineStr"/>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>VADN172</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t>VADN172</t>
+        </is>
+      </c>
       <c r="X8" s="8" t="inlineStr">
         <is>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="Y8" s="8" t="inlineStr"/>
+      <c r="Z8" s="9" t="inlineStr"/>
+      <c r="AA8" s="9" t="inlineStr">
+        <is>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="AB8" s="8" t="inlineStr"/>
+      <c r="AC8" s="8" t="inlineStr">
+        <is>
           <t>VADN172</t>
         </is>
       </c>
-      <c r="Y8" s="8" t="inlineStr">
+      <c r="AD8" s="8" t="inlineStr">
         <is>
           <t>VADN172</t>
         </is>
       </c>
-      <c r="Z8" s="9" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="AA8" s="9" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="AB8" s="8" t="inlineStr"/>
-      <c r="AC8" s="8" t="inlineStr"/>
-      <c r="AD8" s="8" t="inlineStr">
+      <c r="AE8" s="8" t="inlineStr">
         <is>
           <t>VADN172</t>
         </is>
       </c>
-      <c r="AE8" s="8" t="inlineStr">
+      <c r="AF8" s="8" t="inlineStr">
         <is>
           <t>VADN172</t>
         </is>
       </c>
-      <c r="AF8" s="8" t="inlineStr">
-        <is>
-          <t>REF CAL T</t>
-        </is>
-      </c>
-      <c r="AG8" s="9" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
+      <c r="AG8" s="9" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1286,24 +1286,20 @@
       <c r="C9" s="7" t="inlineStr"/>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>VADN023</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr"/>
       <c r="F9" s="9" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>VADN008</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>VADN005</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>VADN030</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr"/>
@@ -1316,74 +1312,78 @@
       <c r="M9" s="9" t="inlineStr"/>
       <c r="N9" s="8" t="inlineStr">
         <is>
+          <t>VADN023</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="inlineStr"/>
+      <c r="R9" s="8" t="inlineStr"/>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="T9" s="9" t="inlineStr"/>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
           <t>VADN008</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
-        <is>
-          <t>VADN023</t>
-        </is>
-      </c>
-      <c r="P9" s="8" t="inlineStr">
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>VADN008</t>
+        </is>
+      </c>
+      <c r="W9" s="8" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="X9" s="8" t="inlineStr"/>
+      <c r="Y9" s="8" t="inlineStr"/>
+      <c r="Z9" s="9" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="AA9" s="9" t="inlineStr"/>
+      <c r="AB9" s="8" t="inlineStr">
+        <is>
+          <t>VADN008</t>
+        </is>
+      </c>
+      <c r="AC9" s="8" t="inlineStr">
+        <is>
+          <t>VADN008</t>
+        </is>
+      </c>
+      <c r="AD9" s="8" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="AE9" s="8" t="inlineStr">
+        <is>
+          <t>VADN008</t>
+        </is>
+      </c>
+      <c r="AF9" s="8" t="inlineStr">
+        <is>
+          <t>VADN008</t>
+        </is>
+      </c>
+      <c r="AG9" s="9" t="inlineStr">
         <is>
           <t>VADN030</t>
-        </is>
-      </c>
-      <c r="Q9" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="R9" s="8" t="inlineStr"/>
-      <c r="S9" s="9" t="inlineStr"/>
-      <c r="T9" s="9" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr"/>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>VADN008</t>
-        </is>
-      </c>
-      <c r="W9" s="8" t="inlineStr">
-        <is>
-          <t>VADN008</t>
-        </is>
-      </c>
-      <c r="X9" s="8" t="inlineStr">
-        <is>
-          <t>VADN008</t>
-        </is>
-      </c>
-      <c r="Y9" s="8" t="inlineStr">
-        <is>
-          <t>VADN008</t>
-        </is>
-      </c>
-      <c r="Z9" s="9" t="inlineStr"/>
-      <c r="AA9" s="9" t="inlineStr"/>
-      <c r="AB9" s="8" t="inlineStr"/>
-      <c r="AC9" s="8" t="inlineStr"/>
-      <c r="AD9" s="8" t="inlineStr">
-        <is>
-          <t>VADN183</t>
-        </is>
-      </c>
-      <c r="AE9" s="8" t="inlineStr">
-        <is>
-          <t>VADN183</t>
-        </is>
-      </c>
-      <c r="AF9" s="8" t="inlineStr">
-        <is>
-          <t>VADN039</t>
-        </is>
-      </c>
-      <c r="AG9" s="9" t="inlineStr">
-        <is>
-          <t>VADN052</t>
         </is>
       </c>
     </row>
@@ -1398,100 +1398,92 @@
           <t>correturno</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>VADN027</t>
-        </is>
-      </c>
+      <c r="C10" s="7" t="inlineStr"/>
       <c r="D10" s="8" t="inlineStr">
         <is>
+          <t>VADN024</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
           <t>VADN031</t>
         </is>
       </c>
-      <c r="E10" s="9" t="inlineStr"/>
       <c r="F10" s="9" t="inlineStr"/>
       <c r="G10" s="8" t="inlineStr">
         <is>
           <t>VADN009</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>VADN031</t>
+          <t>VADN006</t>
         </is>
       </c>
       <c r="K10" s="8" t="inlineStr">
         <is>
-          <t>VADN031</t>
+          <t>VADN006</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>VADN031</t>
+          <t>VADN006</t>
         </is>
       </c>
       <c r="M10" s="9" t="inlineStr"/>
-      <c r="N10" s="8" t="inlineStr"/>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>VADN024</t>
+        </is>
+      </c>
       <c r="O10" s="8" t="inlineStr"/>
       <c r="P10" s="8" t="inlineStr">
         <is>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
           <t>VADN024</t>
         </is>
       </c>
-      <c r="Q10" s="8" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
-      <c r="S10" s="9" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
+      <c r="S10" s="9" t="inlineStr"/>
       <c r="T10" s="9" t="inlineStr"/>
       <c r="U10" s="8" t="inlineStr">
         <is>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="W10" s="8" t="inlineStr"/>
+      <c r="X10" s="8" t="inlineStr"/>
+      <c r="Y10" s="8" t="inlineStr">
+        <is>
+          <t>VADN024</t>
+        </is>
+      </c>
+      <c r="Z10" s="9" t="inlineStr">
+        <is>
           <t>VADN031</t>
         </is>
       </c>
-      <c r="V10" s="8" t="inlineStr"/>
-      <c r="W10" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="X10" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="Y10" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="Z10" s="9" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
       <c r="AA10" s="9" t="inlineStr"/>
-      <c r="AB10" s="8" t="inlineStr"/>
+      <c r="AB10" s="8" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
       <c r="AC10" s="8" t="inlineStr"/>
       <c r="AD10" s="8" t="inlineStr">
         <is>
@@ -1505,12 +1497,12 @@
       </c>
       <c r="AF10" s="8" t="inlineStr">
         <is>
-          <t>VADN153</t>
+          <t>VADN031</t>
         </is>
       </c>
       <c r="AG10" s="9" t="inlineStr">
         <is>
-          <t>VADN031</t>
+          <t>VADN027</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1642,11 @@
           <t>VADN012</t>
         </is>
       </c>
-      <c r="AF11" s="8" t="inlineStr"/>
+      <c r="AF11" s="8" t="inlineStr">
+        <is>
+          <t>VADN012</t>
+        </is>
+      </c>
       <c r="AG11" s="9" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1904,7 +1900,11 @@
           <t>VADN014</t>
         </is>
       </c>
-      <c r="AF13" s="8" t="inlineStr"/>
+      <c r="AF13" s="8" t="inlineStr">
+        <is>
+          <t>VADN014</t>
+        </is>
+      </c>
       <c r="AG13" s="9" t="inlineStr"/>
     </row>
     <row r="14">
@@ -2023,7 +2023,11 @@
           <t>VADN015</t>
         </is>
       </c>
-      <c r="AF14" s="8" t="inlineStr"/>
+      <c r="AF14" s="8" t="inlineStr">
+        <is>
+          <t>VADN015</t>
+        </is>
+      </c>
       <c r="AG14" s="9" t="inlineStr"/>
     </row>
     <row r="15">
@@ -2142,7 +2146,11 @@
           <t>VADN016</t>
         </is>
       </c>
-      <c r="AF15" s="8" t="inlineStr"/>
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>VADN016</t>
+        </is>
+      </c>
       <c r="AG15" s="9" t="inlineStr"/>
     </row>
     <row r="16">
@@ -2261,7 +2269,11 @@
           <t>VADN017</t>
         </is>
       </c>
-      <c r="AF16" s="8" t="inlineStr"/>
+      <c r="AF16" s="8" t="inlineStr">
+        <is>
+          <t>VADN017</t>
+        </is>
+      </c>
       <c r="AG16" s="9" t="inlineStr"/>
     </row>
     <row r="17">
@@ -2380,7 +2392,11 @@
           <t>VADN018</t>
         </is>
       </c>
-      <c r="AF17" s="8" t="inlineStr"/>
+      <c r="AF17" s="8" t="inlineStr">
+        <is>
+          <t>VADN018</t>
+        </is>
+      </c>
       <c r="AG17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
@@ -2499,7 +2515,11 @@
           <t>VADN019</t>
         </is>
       </c>
-      <c r="AF18" s="8" t="inlineStr"/>
+      <c r="AF18" s="8" t="inlineStr">
+        <is>
+          <t>VADN019</t>
+        </is>
+      </c>
       <c r="AG18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
@@ -2618,7 +2638,11 @@
           <t>VADN020</t>
         </is>
       </c>
-      <c r="AF19" s="8" t="inlineStr"/>
+      <c r="AF19" s="8" t="inlineStr">
+        <is>
+          <t>VADN020</t>
+        </is>
+      </c>
       <c r="AG19" s="9" t="inlineStr"/>
     </row>
     <row r="20">
@@ -2737,7 +2761,11 @@
           <t>VADN021</t>
         </is>
       </c>
-      <c r="AF20" s="8" t="inlineStr"/>
+      <c r="AF20" s="8" t="inlineStr">
+        <is>
+          <t>VADN021</t>
+        </is>
+      </c>
       <c r="AG20" s="9" t="inlineStr"/>
     </row>
     <row r="21">
@@ -2752,7 +2780,11 @@
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr"/>
-      <c r="D21" s="8" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>VADN023</t>
+        </is>
+      </c>
       <c r="E21" s="9" t="inlineStr"/>
       <c r="F21" s="9" t="inlineStr"/>
       <c r="G21" s="8" t="inlineStr">
@@ -2778,12 +2810,12 @@
       </c>
       <c r="L21" s="9" t="inlineStr"/>
       <c r="M21" s="9" t="inlineStr"/>
-      <c r="N21" s="8" t="inlineStr">
+      <c r="N21" s="8" t="inlineStr"/>
+      <c r="O21" s="8" t="inlineStr">
         <is>
           <t>VADN023</t>
         </is>
       </c>
-      <c r="O21" s="8" t="inlineStr"/>
       <c r="P21" s="8" t="inlineStr">
         <is>
           <t>VADN023</t>
@@ -2825,7 +2857,11 @@
       <c r="Z21" s="9" t="inlineStr"/>
       <c r="AA21" s="9" t="inlineStr"/>
       <c r="AB21" s="8" t="inlineStr"/>
-      <c r="AC21" s="8" t="inlineStr"/>
+      <c r="AC21" s="8" t="inlineStr">
+        <is>
+          <t>VADN023</t>
+        </is>
+      </c>
       <c r="AD21" s="8" t="inlineStr">
         <is>
           <t>VADN023</t>
@@ -2855,11 +2891,7 @@
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>VADN024</t>
-        </is>
-      </c>
+      <c r="D22" s="8" t="inlineStr"/>
       <c r="E22" s="9" t="inlineStr"/>
       <c r="F22" s="9" t="inlineStr"/>
       <c r="G22" s="8" t="inlineStr">
@@ -2868,7 +2900,11 @@
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="8" t="inlineStr"/>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>VADN024</t>
+        </is>
+      </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
           <t>VADN024</t>
@@ -2881,27 +2917,23 @@
       </c>
       <c r="L22" s="9" t="inlineStr"/>
       <c r="M22" s="9" t="inlineStr"/>
-      <c r="N22" s="8" t="inlineStr">
+      <c r="N22" s="8" t="inlineStr"/>
+      <c r="O22" s="8" t="inlineStr">
         <is>
           <t>VADN024</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="P22" s="8" t="inlineStr">
         <is>
           <t>VADN024</t>
         </is>
       </c>
-      <c r="P22" s="8" t="inlineStr"/>
       <c r="Q22" s="8" t="inlineStr">
         <is>
           <t>VADN024</t>
         </is>
       </c>
-      <c r="R22" s="8" t="inlineStr">
-        <is>
-          <t>VADN024</t>
-        </is>
-      </c>
+      <c r="R22" s="8" t="inlineStr"/>
       <c r="S22" s="9" t="inlineStr"/>
       <c r="T22" s="9" t="inlineStr"/>
       <c r="U22" s="8" t="inlineStr">
@@ -2914,17 +2946,17 @@
           <t>VADN024</t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr"/>
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t>VADN024</t>
+        </is>
+      </c>
       <c r="X22" s="8" t="inlineStr">
         <is>
           <t>VADN024</t>
         </is>
       </c>
-      <c r="Y22" s="8" t="inlineStr">
-        <is>
-          <t>VADN024</t>
-        </is>
-      </c>
+      <c r="Y22" s="8" t="inlineStr"/>
       <c r="Z22" s="9" t="inlineStr"/>
       <c r="AA22" s="9" t="inlineStr"/>
       <c r="AB22" s="8" t="inlineStr">
@@ -3062,7 +3094,11 @@
           <t>VADN033</t>
         </is>
       </c>
-      <c r="AF23" s="8" t="inlineStr"/>
+      <c r="AF23" s="8" t="inlineStr">
+        <is>
+          <t>VADN033</t>
+        </is>
+      </c>
       <c r="AG23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
@@ -3191,8 +3227,16 @@
           <t>VADN035</t>
         </is>
       </c>
-      <c r="AD24" s="8" t="inlineStr"/>
-      <c r="AE24" s="8" t="inlineStr"/>
+      <c r="AD24" s="8" t="inlineStr">
+        <is>
+          <t>VADN035</t>
+        </is>
+      </c>
+      <c r="AE24" s="8" t="inlineStr">
+        <is>
+          <t>VADN035</t>
+        </is>
+      </c>
       <c r="AF24" s="8" t="inlineStr">
         <is>
           <t>VADN035</t>
@@ -3451,7 +3495,11 @@
           <t>VADN037</t>
         </is>
       </c>
-      <c r="AF26" s="8" t="inlineStr"/>
+      <c r="AF26" s="8" t="inlineStr">
+        <is>
+          <t>VADN037</t>
+        </is>
+      </c>
       <c r="AG26" s="9" t="inlineStr"/>
     </row>
     <row r="27">
@@ -3570,7 +3618,11 @@
           <t>VADN039</t>
         </is>
       </c>
-      <c r="AF27" s="8" t="inlineStr"/>
+      <c r="AF27" s="8" t="inlineStr">
+        <is>
+          <t>VADN039</t>
+        </is>
+      </c>
       <c r="AG27" s="9" t="inlineStr"/>
     </row>
     <row r="28">
@@ -3689,7 +3741,11 @@
           <t>VADP001</t>
         </is>
       </c>
-      <c r="AF28" s="8" t="inlineStr"/>
+      <c r="AF28" s="8" t="inlineStr">
+        <is>
+          <t>VADP001</t>
+        </is>
+      </c>
       <c r="AG28" s="9" t="inlineStr"/>
     </row>
     <row r="29">
@@ -3808,7 +3864,11 @@
           <t>VADP002</t>
         </is>
       </c>
-      <c r="AF29" s="8" t="inlineStr"/>
+      <c r="AF29" s="8" t="inlineStr">
+        <is>
+          <t>VADP002</t>
+        </is>
+      </c>
       <c r="AG29" s="9" t="inlineStr"/>
     </row>
     <row r="30">
@@ -3927,7 +3987,11 @@
           <t>H</t>
         </is>
       </c>
-      <c r="AF30" s="8" t="inlineStr"/>
+      <c r="AF30" s="8" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="AG30" s="9" t="inlineStr"/>
     </row>
     <row r="31">
@@ -4046,7 +4110,11 @@
           <t>REF CAL M</t>
         </is>
       </c>
-      <c r="AF31" s="8" t="inlineStr"/>
+      <c r="AF31" s="8" t="inlineStr">
+        <is>
+          <t>REF CAL M</t>
+        </is>
+      </c>
       <c r="AG31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
@@ -4165,7 +4233,11 @@
           <t>REF CAL T</t>
         </is>
       </c>
-      <c r="AF32" s="8" t="inlineStr"/>
+      <c r="AF32" s="8" t="inlineStr">
+        <is>
+          <t>REF CAL T</t>
+        </is>
+      </c>
       <c r="AG32" s="9" t="inlineStr"/>
     </row>
     <row r="33">
@@ -4284,7 +4356,11 @@
           <t>VADN151</t>
         </is>
       </c>
-      <c r="AF33" s="8" t="inlineStr"/>
+      <c r="AF33" s="8" t="inlineStr">
+        <is>
+          <t>VADN151</t>
+        </is>
+      </c>
       <c r="AG33" s="9" t="inlineStr"/>
     </row>
     <row r="34">
@@ -4403,7 +4479,11 @@
           <t>VADN153</t>
         </is>
       </c>
-      <c r="AF34" s="8" t="inlineStr"/>
+      <c r="AF34" s="8" t="inlineStr">
+        <is>
+          <t>VADN153</t>
+        </is>
+      </c>
       <c r="AG34" s="9" t="inlineStr"/>
     </row>
     <row r="35">
@@ -4522,7 +4602,11 @@
           <t>VADN161</t>
         </is>
       </c>
-      <c r="AF35" s="8" t="inlineStr"/>
+      <c r="AF35" s="8" t="inlineStr">
+        <is>
+          <t>VADN161</t>
+        </is>
+      </c>
       <c r="AG35" s="9" t="inlineStr"/>
     </row>
     <row r="36">
@@ -4641,7 +4725,11 @@
           <t>VADN164</t>
         </is>
       </c>
-      <c r="AF36" s="8" t="inlineStr"/>
+      <c r="AF36" s="8" t="inlineStr">
+        <is>
+          <t>VADN164</t>
+        </is>
+      </c>
       <c r="AG36" s="9" t="inlineStr"/>
     </row>
     <row r="37">
@@ -4780,7 +4868,11 @@
           <t>VADN171</t>
         </is>
       </c>
-      <c r="AF37" s="8" t="inlineStr"/>
+      <c r="AF37" s="8" t="inlineStr">
+        <is>
+          <t>VADN171</t>
+        </is>
+      </c>
       <c r="AG37" s="9" t="inlineStr"/>
     </row>
     <row r="38">
@@ -5034,7 +5126,11 @@
           <t>VADN174</t>
         </is>
       </c>
-      <c r="AF39" s="8" t="inlineStr"/>
+      <c r="AF39" s="8" t="inlineStr">
+        <is>
+          <t>VADN174</t>
+        </is>
+      </c>
       <c r="AG39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
@@ -5153,7 +5249,11 @@
           <t>VADN175</t>
         </is>
       </c>
-      <c r="AF40" s="8" t="inlineStr"/>
+      <c r="AF40" s="8" t="inlineStr">
+        <is>
+          <t>VADN175</t>
+        </is>
+      </c>
       <c r="AG40" s="9" t="inlineStr"/>
     </row>
     <row r="41">
@@ -5214,53 +5314,57 @@
           <t>VADN176</t>
         </is>
       </c>
-      <c r="R41" s="8" t="inlineStr"/>
+      <c r="R41" s="8" t="inlineStr">
+        <is>
+          <t>VADN176</t>
+        </is>
+      </c>
       <c r="S41" s="9" t="inlineStr"/>
       <c r="T41" s="9" t="inlineStr"/>
-      <c r="U41" s="8" t="inlineStr">
+      <c r="U41" s="8" t="inlineStr"/>
+      <c r="V41" s="8" t="inlineStr">
         <is>
           <t>VADN176</t>
         </is>
       </c>
-      <c r="V41" s="8" t="inlineStr">
+      <c r="W41" s="8" t="inlineStr">
         <is>
           <t>VADN176</t>
         </is>
       </c>
-      <c r="W41" s="8" t="inlineStr">
+      <c r="X41" s="8" t="inlineStr">
         <is>
           <t>VADN176</t>
         </is>
       </c>
-      <c r="X41" s="8" t="inlineStr">
+      <c r="Y41" s="8" t="inlineStr">
         <is>
           <t>VADN176</t>
         </is>
       </c>
-      <c r="Y41" s="8" t="inlineStr"/>
       <c r="Z41" s="9" t="inlineStr"/>
       <c r="AA41" s="9" t="inlineStr"/>
-      <c r="AB41" s="8" t="inlineStr">
+      <c r="AB41" s="8" t="inlineStr"/>
+      <c r="AC41" s="8" t="inlineStr">
         <is>
           <t>VADN176</t>
         </is>
       </c>
-      <c r="AC41" s="8" t="inlineStr">
+      <c r="AD41" s="8" t="inlineStr">
         <is>
           <t>VADN176</t>
         </is>
       </c>
-      <c r="AD41" s="8" t="inlineStr">
+      <c r="AE41" s="8" t="inlineStr">
         <is>
           <t>VADN176</t>
         </is>
       </c>
-      <c r="AE41" s="8" t="inlineStr">
+      <c r="AF41" s="8" t="inlineStr">
         <is>
           <t>VADN176</t>
         </is>
       </c>
-      <c r="AF41" s="8" t="inlineStr"/>
       <c r="AG41" s="9" t="inlineStr"/>
     </row>
     <row r="42">
@@ -5379,7 +5483,11 @@
           <t>VADN178</t>
         </is>
       </c>
-      <c r="AF42" s="8" t="inlineStr"/>
+      <c r="AF42" s="8" t="inlineStr">
+        <is>
+          <t>VADN178</t>
+        </is>
+      </c>
       <c r="AG42" s="9" t="inlineStr"/>
     </row>
     <row r="43">
@@ -5498,7 +5606,11 @@
           <t>VADN179</t>
         </is>
       </c>
-      <c r="AF43" s="8" t="inlineStr"/>
+      <c r="AF43" s="8" t="inlineStr">
+        <is>
+          <t>VADN179</t>
+        </is>
+      </c>
       <c r="AG43" s="9" t="inlineStr"/>
     </row>
     <row r="44">
@@ -5617,7 +5729,11 @@
           <t>VADN182</t>
         </is>
       </c>
-      <c r="AF44" s="8" t="inlineStr"/>
+      <c r="AF44" s="8" t="inlineStr">
+        <is>
+          <t>VADN182</t>
+        </is>
+      </c>
       <c r="AG44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
@@ -5726,8 +5842,16 @@
           <t>VADN183</t>
         </is>
       </c>
-      <c r="AD45" s="8" t="inlineStr"/>
-      <c r="AE45" s="8" t="inlineStr"/>
+      <c r="AD45" s="8" t="inlineStr">
+        <is>
+          <t>VADN183</t>
+        </is>
+      </c>
+      <c r="AE45" s="8" t="inlineStr">
+        <is>
+          <t>VADN183</t>
+        </is>
+      </c>
       <c r="AF45" s="8" t="inlineStr">
         <is>
           <t>VADN183</t>
@@ -5851,7 +5975,11 @@
           <t>VADN191</t>
         </is>
       </c>
-      <c r="AF46" s="8" t="inlineStr"/>
+      <c r="AF46" s="8" t="inlineStr">
+        <is>
+          <t>VADN191</t>
+        </is>
+      </c>
       <c r="AG46" s="9" t="inlineStr"/>
     </row>
     <row r="47">
@@ -5970,7 +6098,11 @@
           <t>VADN192</t>
         </is>
       </c>
-      <c r="AF47" s="8" t="inlineStr"/>
+      <c r="AF47" s="8" t="inlineStr">
+        <is>
+          <t>VADN192</t>
+        </is>
+      </c>
       <c r="AG47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
@@ -6089,7 +6221,11 @@
           <t>VADN193</t>
         </is>
       </c>
-      <c r="AF48" s="8" t="inlineStr"/>
+      <c r="AF48" s="8" t="inlineStr">
+        <is>
+          <t>VADN193</t>
+        </is>
+      </c>
       <c r="AG48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
@@ -6208,7 +6344,11 @@
           <t>VADN195</t>
         </is>
       </c>
-      <c r="AF49" s="8" t="inlineStr"/>
+      <c r="AF49" s="8" t="inlineStr">
+        <is>
+          <t>VADN195</t>
+        </is>
+      </c>
       <c r="AG49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
@@ -6228,11 +6368,7 @@
           <t>VADN007</t>
         </is>
       </c>
-      <c r="E50" s="9" t="inlineStr">
-        <is>
-          <t>VADN001</t>
-        </is>
-      </c>
+      <c r="E50" s="9" t="inlineStr"/>
       <c r="F50" s="9" t="inlineStr"/>
       <c r="G50" s="10" t="inlineStr">
         <is>
@@ -6351,7 +6487,11 @@
           <t>VADN007</t>
         </is>
       </c>
-      <c r="AF50" s="8" t="inlineStr"/>
+      <c r="AF50" s="8" t="inlineStr">
+        <is>
+          <t>VADN007</t>
+        </is>
+      </c>
       <c r="AG50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
@@ -6371,13 +6511,13 @@
           <t>VADN008</t>
         </is>
       </c>
-      <c r="E51" s="9" t="inlineStr"/>
+      <c r="E51" s="9" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
       <c r="F51" s="9" t="inlineStr"/>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>VADN008</t>
-        </is>
-      </c>
+      <c r="G51" s="8" t="inlineStr"/>
       <c r="H51" s="7" t="inlineStr"/>
       <c r="I51" s="8" t="inlineStr">
         <is>
@@ -6400,7 +6540,11 @@
         </is>
       </c>
       <c r="M51" s="9" t="inlineStr"/>
-      <c r="N51" s="8" t="inlineStr"/>
+      <c r="N51" s="8" t="inlineStr">
+        <is>
+          <t>VADN008</t>
+        </is>
+      </c>
       <c r="O51" s="8" t="inlineStr">
         <is>
           <t>VADN008</t>
@@ -6421,11 +6565,7 @@
           <t>VADN008</t>
         </is>
       </c>
-      <c r="S51" s="9" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
+      <c r="S51" s="9" t="inlineStr"/>
       <c r="T51" s="9" t="inlineStr"/>
       <c r="U51" s="10" t="inlineStr">
         <is>
@@ -6510,11 +6650,7 @@
           <t>VADN009</t>
         </is>
       </c>
-      <c r="E52" s="9" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
+      <c r="E52" s="9" t="inlineStr"/>
       <c r="F52" s="9" t="inlineStr"/>
       <c r="G52" s="8" t="inlineStr"/>
       <c r="H52" s="7" t="inlineStr"/>
@@ -6591,14 +6727,18 @@
           <t>VADN009</t>
         </is>
       </c>
-      <c r="Z52" s="9" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
+      <c r="Z52" s="9" t="inlineStr"/>
       <c r="AA52" s="9" t="inlineStr"/>
-      <c r="AB52" s="8" t="inlineStr"/>
-      <c r="AC52" s="8" t="inlineStr"/>
+      <c r="AB52" s="8" t="inlineStr">
+        <is>
+          <t>VADN009</t>
+        </is>
+      </c>
+      <c r="AC52" s="8" t="inlineStr">
+        <is>
+          <t>VADN009</t>
+        </is>
+      </c>
       <c r="AD52" s="8" t="inlineStr">
         <is>
           <t>VADN009</t>
@@ -6632,12 +6772,12 @@
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr"/>
-      <c r="D53" s="8" t="inlineStr"/>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>VADN010</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr"/>
       <c r="F53" s="9" t="inlineStr"/>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -6736,8 +6876,16 @@
           <t>VADN010</t>
         </is>
       </c>
-      <c r="AF53" s="8" t="inlineStr"/>
-      <c r="AG53" s="9" t="inlineStr"/>
+      <c r="AF53" s="8" t="inlineStr">
+        <is>
+          <t>VADN010</t>
+        </is>
+      </c>
+      <c r="AG53" s="9" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -6833,14 +6981,18 @@
           <t>VADN011</t>
         </is>
       </c>
-      <c r="Z54" s="9" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
+      <c r="Z54" s="9" t="inlineStr"/>
       <c r="AA54" s="9" t="inlineStr"/>
-      <c r="AB54" s="8" t="inlineStr"/>
-      <c r="AC54" s="8" t="inlineStr"/>
+      <c r="AB54" s="8" t="inlineStr">
+        <is>
+          <t>VADN011</t>
+        </is>
+      </c>
+      <c r="AC54" s="8" t="inlineStr">
+        <is>
+          <t>VADN011</t>
+        </is>
+      </c>
       <c r="AD54" s="8" t="inlineStr">
         <is>
           <t>VADN011</t>
@@ -6856,11 +7008,7 @@
           <t>VADN011</t>
         </is>
       </c>
-      <c r="AG54" s="9" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
+      <c r="AG54" s="9" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -6878,11 +7026,7 @@
           <t>VADN162</t>
         </is>
       </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>VADN162</t>
-        </is>
-      </c>
+      <c r="D55" s="8" t="inlineStr"/>
       <c r="E55" s="9" t="inlineStr"/>
       <c r="F55" s="9" t="inlineStr"/>
       <c r="G55" s="8" t="inlineStr">
@@ -6890,11 +7034,7 @@
           <t>VADN162</t>
         </is>
       </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>VADN162</t>
-        </is>
-      </c>
+      <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="8" t="inlineStr"/>
       <c r="J55" s="8" t="inlineStr"/>
       <c r="K55" s="8" t="inlineStr">
@@ -6908,7 +7048,11 @@
         </is>
       </c>
       <c r="M55" s="9" t="inlineStr"/>
-      <c r="N55" s="8" t="inlineStr"/>
+      <c r="N55" s="8" t="inlineStr">
+        <is>
+          <t>VADN162</t>
+        </is>
+      </c>
       <c r="O55" s="8" t="inlineStr">
         <is>
           <t>VADN162</t>
@@ -6921,16 +7065,24 @@
       </c>
       <c r="Q55" s="8" t="inlineStr"/>
       <c r="R55" s="8" t="inlineStr"/>
-      <c r="S55" s="9" t="inlineStr"/>
+      <c r="S55" s="9" t="inlineStr">
+        <is>
+          <t>VADN162</t>
+        </is>
+      </c>
       <c r="T55" s="9" t="inlineStr"/>
-      <c r="U55" s="8" t="inlineStr"/>
-      <c r="V55" s="8" t="inlineStr"/>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>VADN162</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>VADN162</t>
+        </is>
+      </c>
       <c r="W55" s="8" t="inlineStr"/>
-      <c r="X55" s="8" t="inlineStr">
-        <is>
-          <t>VADN162</t>
-        </is>
-      </c>
+      <c r="X55" s="8" t="inlineStr"/>
       <c r="Y55" s="8" t="inlineStr">
         <is>
           <t>VADN162</t>
@@ -6962,7 +7114,11 @@
           <t>VADN162</t>
         </is>
       </c>
-      <c r="AF55" s="8" t="inlineStr"/>
+      <c r="AF55" s="8" t="inlineStr">
+        <is>
+          <t>VADN162</t>
+        </is>
+      </c>
       <c r="AG55" s="9" t="inlineStr"/>
     </row>
     <row r="56">
@@ -6977,21 +7133,29 @@
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr"/>
-      <c r="D56" s="8" t="inlineStr"/>
-      <c r="E56" s="9" t="inlineStr"/>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>VADN162</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="inlineStr">
+        <is>
+          <t>VADN162</t>
+        </is>
+      </c>
       <c r="F56" s="9" t="inlineStr"/>
       <c r="G56" s="8" t="inlineStr"/>
-      <c r="H56" s="7" t="inlineStr"/>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>VADN162</t>
+        </is>
+      </c>
       <c r="I56" s="8" t="inlineStr"/>
       <c r="J56" s="8" t="inlineStr"/>
       <c r="K56" s="8" t="inlineStr"/>
       <c r="L56" s="9" t="inlineStr"/>
       <c r="M56" s="9" t="inlineStr"/>
-      <c r="N56" s="8" t="inlineStr">
-        <is>
-          <t>VADN162</t>
-        </is>
-      </c>
+      <c r="N56" s="8" t="inlineStr"/>
       <c r="O56" s="8" t="inlineStr"/>
       <c r="P56" s="8" t="inlineStr"/>
       <c r="Q56" s="8" t="inlineStr">
@@ -7006,22 +7170,18 @@
       </c>
       <c r="S56" s="9" t="inlineStr"/>
       <c r="T56" s="9" t="inlineStr"/>
-      <c r="U56" s="8" t="inlineStr">
+      <c r="U56" s="8" t="inlineStr"/>
+      <c r="V56" s="8" t="inlineStr"/>
+      <c r="W56" s="8" t="inlineStr">
         <is>
           <t>VADN162</t>
         </is>
       </c>
-      <c r="V56" s="8" t="inlineStr">
+      <c r="X56" s="8" t="inlineStr">
         <is>
           <t>VADN162</t>
         </is>
       </c>
-      <c r="W56" s="8" t="inlineStr">
-        <is>
-          <t>VADN162</t>
-        </is>
-      </c>
-      <c r="X56" s="8" t="inlineStr"/>
       <c r="Y56" s="8" t="inlineStr"/>
       <c r="Z56" s="9" t="inlineStr"/>
       <c r="AA56" s="9" t="inlineStr"/>
@@ -7029,16 +7189,8 @@
       <c r="AC56" s="8" t="inlineStr"/>
       <c r="AD56" s="8" t="inlineStr"/>
       <c r="AE56" s="8" t="inlineStr"/>
-      <c r="AF56" s="8" t="inlineStr">
-        <is>
-          <t>VADN162</t>
-        </is>
-      </c>
-      <c r="AG56" s="9" t="inlineStr">
-        <is>
-          <t>VADN162</t>
-        </is>
-      </c>
+      <c r="AF56" s="8" t="inlineStr"/>
+      <c r="AG56" s="9" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -7053,11 +7205,7 @@
       </c>
       <c r="C57" s="7" t="inlineStr"/>
       <c r="D57" s="8" t="inlineStr"/>
-      <c r="E57" s="9" t="inlineStr">
-        <is>
-          <t>VADN162</t>
-        </is>
-      </c>
+      <c r="E57" s="9" t="inlineStr"/>
       <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="8" t="inlineStr"/>
       <c r="H57" s="7" t="inlineStr"/>
@@ -7079,11 +7227,7 @@
       <c r="P57" s="8" t="inlineStr"/>
       <c r="Q57" s="8" t="inlineStr"/>
       <c r="R57" s="8" t="inlineStr"/>
-      <c r="S57" s="9" t="inlineStr">
-        <is>
-          <t>VADN162</t>
-        </is>
-      </c>
+      <c r="S57" s="9" t="inlineStr"/>
       <c r="T57" s="9" t="inlineStr"/>
       <c r="U57" s="8" t="inlineStr"/>
       <c r="V57" s="8" t="inlineStr"/>
@@ -7097,7 +7241,11 @@
       <c r="AD57" s="8" t="inlineStr"/>
       <c r="AE57" s="8" t="inlineStr"/>
       <c r="AF57" s="8" t="inlineStr"/>
-      <c r="AG57" s="9" t="inlineStr"/>
+      <c r="AG57" s="9" t="inlineStr">
+        <is>
+          <t>VADN162</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -7112,7 +7260,11 @@
       </c>
       <c r="C58" s="7" t="inlineStr"/>
       <c r="D58" s="8" t="inlineStr"/>
-      <c r="E58" s="9" t="inlineStr"/>
+      <c r="E58" s="9" t="inlineStr">
+        <is>
+          <t>VADN194</t>
+        </is>
+      </c>
       <c r="F58" s="9" t="inlineStr"/>
       <c r="G58" s="8" t="inlineStr"/>
       <c r="H58" s="7" t="inlineStr"/>
@@ -7171,11 +7323,7 @@
       </c>
       <c r="C59" s="7" t="inlineStr"/>
       <c r="D59" s="8" t="inlineStr"/>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>VADN194</t>
-        </is>
-      </c>
+      <c r="E59" s="9" t="inlineStr"/>
       <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="8" t="inlineStr"/>
       <c r="H59" s="7" t="inlineStr"/>
@@ -7221,8 +7369,16 @@
           <t>VADN181</t>
         </is>
       </c>
-      <c r="D60" s="8" t="inlineStr"/>
-      <c r="E60" s="9" t="inlineStr"/>
+      <c r="D60" s="8" t="inlineStr">
+        <is>
+          <t>VADN181</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>VADN181</t>
+        </is>
+      </c>
       <c r="F60" s="9" t="inlineStr"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -7234,17 +7390,13 @@
           <t>VADN181</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr"/>
+      <c r="J60" s="8" t="inlineStr"/>
+      <c r="K60" s="8" t="inlineStr">
         <is>
           <t>VADN181</t>
         </is>
       </c>
-      <c r="J60" s="8" t="inlineStr">
-        <is>
-          <t>VADN181</t>
-        </is>
-      </c>
-      <c r="K60" s="8" t="inlineStr"/>
       <c r="L60" s="9" t="inlineStr">
         <is>
           <t>VADN181</t>
@@ -7286,39 +7438,39 @@
       </c>
       <c r="W60" s="8" t="inlineStr">
         <is>
+          <t>VADN173</t>
+        </is>
+      </c>
+      <c r="X60" s="8" t="inlineStr"/>
+      <c r="Y60" s="8" t="inlineStr"/>
+      <c r="Z60" s="9" t="inlineStr"/>
+      <c r="AA60" s="9" t="inlineStr"/>
+      <c r="AB60" s="8" t="inlineStr">
+        <is>
           <t>VADN181</t>
         </is>
       </c>
-      <c r="X60" s="8" t="inlineStr">
+      <c r="AC60" s="8" t="inlineStr">
         <is>
           <t>VADN181</t>
         </is>
       </c>
-      <c r="Y60" s="8" t="inlineStr"/>
-      <c r="Z60" s="9" t="inlineStr">
+      <c r="AD60" s="8" t="inlineStr">
         <is>
           <t>VADN181</t>
         </is>
       </c>
-      <c r="AA60" s="9" t="inlineStr"/>
-      <c r="AB60" s="8" t="inlineStr"/>
-      <c r="AC60" s="8" t="inlineStr">
+      <c r="AE60" s="8" t="inlineStr">
         <is>
           <t>VADN181</t>
         </is>
       </c>
-      <c r="AD60" s="8" t="inlineStr"/>
-      <c r="AE60" s="8" t="inlineStr"/>
       <c r="AF60" s="8" t="inlineStr">
         <is>
           <t>VADN181</t>
         </is>
       </c>
-      <c r="AG60" s="9" t="inlineStr">
-        <is>
-          <t>VADN173</t>
-        </is>
-      </c>
+      <c r="AG60" s="9" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -7332,24 +7484,28 @@
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr"/>
-      <c r="D61" s="8" t="inlineStr"/>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>VADN173</t>
+        </is>
+      </c>
       <c r="E61" s="9" t="inlineStr"/>
       <c r="F61" s="9" t="inlineStr"/>
-      <c r="G61" s="8" t="inlineStr">
+      <c r="G61" s="8" t="inlineStr"/>
+      <c r="H61" s="7" t="inlineStr"/>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>VADN181</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
+          <t>VADN181</t>
+        </is>
+      </c>
+      <c r="K61" s="8" t="inlineStr">
         <is>
           <t>VADN173</t>
-        </is>
-      </c>
-      <c r="H61" s="7" t="inlineStr"/>
-      <c r="I61" s="8" t="inlineStr"/>
-      <c r="J61" s="8" t="inlineStr">
-        <is>
-          <t>VADN173</t>
-        </is>
-      </c>
-      <c r="K61" s="8" t="inlineStr">
-        <is>
-          <t>VADN181</t>
         </is>
       </c>
       <c r="L61" s="9" t="inlineStr">
@@ -7360,20 +7516,24 @@
       <c r="M61" s="9" t="inlineStr"/>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>VADN181</t>
-        </is>
-      </c>
-      <c r="O61" s="8" t="inlineStr"/>
-      <c r="P61" s="8" t="inlineStr"/>
+          <t>VADN173</t>
+        </is>
+      </c>
+      <c r="O61" s="8" t="inlineStr">
+        <is>
+          <t>VADN173</t>
+        </is>
+      </c>
+      <c r="P61" s="8" t="inlineStr">
+        <is>
+          <t>VADN173</t>
+        </is>
+      </c>
       <c r="Q61" s="8" t="inlineStr"/>
-      <c r="R61" s="8" t="inlineStr">
-        <is>
-          <t>VADN181</t>
-        </is>
-      </c>
+      <c r="R61" s="8" t="inlineStr"/>
       <c r="S61" s="9" t="inlineStr">
         <is>
-          <t>VADN181</t>
+          <t>VADN173</t>
         </is>
       </c>
       <c r="T61" s="9" t="inlineStr"/>
@@ -7387,37 +7547,25 @@
           <t>VADN173</t>
         </is>
       </c>
-      <c r="W61" s="8" t="inlineStr">
-        <is>
-          <t>VADN173</t>
-        </is>
-      </c>
+      <c r="W61" s="8" t="inlineStr"/>
       <c r="X61" s="8" t="inlineStr"/>
-      <c r="Y61" s="8" t="inlineStr">
-        <is>
-          <t>VADN173</t>
-        </is>
-      </c>
-      <c r="Z61" s="9" t="inlineStr"/>
+      <c r="Y61" s="8" t="inlineStr"/>
+      <c r="Z61" s="9" t="inlineStr">
+        <is>
+          <t>VADN181</t>
+        </is>
+      </c>
       <c r="AA61" s="9" t="inlineStr"/>
       <c r="AB61" s="8" t="inlineStr"/>
       <c r="AC61" s="8" t="inlineStr"/>
-      <c r="AD61" s="8" t="inlineStr">
-        <is>
-          <t>VADN181</t>
-        </is>
-      </c>
-      <c r="AE61" s="8" t="inlineStr">
-        <is>
-          <t>VADN181</t>
-        </is>
-      </c>
-      <c r="AF61" s="8" t="inlineStr">
+      <c r="AD61" s="8" t="inlineStr"/>
+      <c r="AE61" s="8" t="inlineStr"/>
+      <c r="AF61" s="8" t="inlineStr"/>
+      <c r="AG61" s="9" t="inlineStr">
         <is>
           <t>VADN173</t>
         </is>
       </c>
-      <c r="AG61" s="9" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -7430,19 +7578,19 @@
           <t>PAT_MED</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>VADN181</t>
-        </is>
-      </c>
-      <c r="E62" s="9" t="inlineStr">
-        <is>
-          <t>VADN181</t>
-        </is>
-      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>VADN173</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr"/>
+      <c r="E62" s="9" t="inlineStr"/>
       <c r="F62" s="9" t="inlineStr"/>
-      <c r="G62" s="8" t="inlineStr"/>
+      <c r="G62" s="8" t="inlineStr">
+        <is>
+          <t>VADN173</t>
+        </is>
+      </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
           <t>VADN173</t>
@@ -7453,38 +7601,34 @@
           <t>VADN173</t>
         </is>
       </c>
-      <c r="J62" s="8" t="inlineStr"/>
-      <c r="K62" s="8" t="inlineStr">
+      <c r="J62" s="8" t="inlineStr">
         <is>
           <t>VADN173</t>
         </is>
       </c>
+      <c r="K62" s="8" t="inlineStr"/>
       <c r="L62" s="9" t="inlineStr"/>
       <c r="M62" s="9" t="inlineStr"/>
       <c r="N62" s="8" t="inlineStr">
         <is>
+          <t>VADN181</t>
+        </is>
+      </c>
+      <c r="O62" s="8" t="inlineStr"/>
+      <c r="P62" s="8" t="inlineStr"/>
+      <c r="Q62" s="8" t="inlineStr">
+        <is>
           <t>VADN173</t>
         </is>
       </c>
-      <c r="O62" s="8" t="inlineStr">
-        <is>
-          <t>VADN173</t>
-        </is>
-      </c>
-      <c r="P62" s="8" t="inlineStr">
-        <is>
-          <t>VADN173</t>
-        </is>
-      </c>
-      <c r="Q62" s="8" t="inlineStr">
-        <is>
-          <t>VADN173</t>
-        </is>
-      </c>
-      <c r="R62" s="8" t="inlineStr"/>
+      <c r="R62" s="8" t="inlineStr">
+        <is>
+          <t>VADN181</t>
+        </is>
+      </c>
       <c r="S62" s="9" t="inlineStr">
         <is>
-          <t>VADN173</t>
+          <t>VADN181</t>
         </is>
       </c>
       <c r="T62" s="9" t="inlineStr"/>
@@ -7496,7 +7640,11 @@
           <t>VADN173</t>
         </is>
       </c>
-      <c r="Y62" s="8" t="inlineStr"/>
+      <c r="Y62" s="8" t="inlineStr">
+        <is>
+          <t>VADN181</t>
+        </is>
+      </c>
       <c r="Z62" s="9" t="inlineStr">
         <is>
           <t>VADN173</t>
@@ -7505,20 +7653,20 @@
       <c r="AA62" s="9" t="inlineStr"/>
       <c r="AB62" s="8" t="inlineStr">
         <is>
-          <t>VADN181</t>
-        </is>
-      </c>
-      <c r="AC62" s="8" t="inlineStr">
-        <is>
           <t>VADN173</t>
         </is>
       </c>
+      <c r="AC62" s="8" t="inlineStr"/>
       <c r="AD62" s="8" t="inlineStr">
         <is>
           <t>VADN173</t>
         </is>
       </c>
-      <c r="AE62" s="8" t="inlineStr"/>
+      <c r="AE62" s="8" t="inlineStr">
+        <is>
+          <t>VADN173</t>
+        </is>
+      </c>
       <c r="AF62" s="8" t="inlineStr"/>
       <c r="AG62" s="9" t="inlineStr">
         <is>
@@ -7537,16 +7685,8 @@
           <t>PAT_MED</t>
         </is>
       </c>
-      <c r="C63" s="7" t="inlineStr">
-        <is>
-          <t>VADN173</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>VADN173</t>
-        </is>
-      </c>
+      <c r="C63" s="7" t="inlineStr"/>
+      <c r="D63" s="8" t="inlineStr"/>
       <c r="E63" s="9" t="inlineStr">
         <is>
           <t>VADN173</t>
@@ -7629,28 +7769,36 @@
         </is>
       </c>
       <c r="V63" s="8" t="inlineStr"/>
-      <c r="W63" s="8" t="inlineStr"/>
-      <c r="X63" s="8" t="inlineStr"/>
+      <c r="W63" s="8" t="inlineStr">
+        <is>
+          <t>VADN181</t>
+        </is>
+      </c>
+      <c r="X63" s="8" t="inlineStr">
+        <is>
+          <t>VADN181</t>
+        </is>
+      </c>
       <c r="Y63" s="8" t="inlineStr">
         <is>
-          <t>VADN181</t>
+          <t>VADN173</t>
         </is>
       </c>
       <c r="Z63" s="9" t="inlineStr"/>
       <c r="AA63" s="9" t="inlineStr"/>
-      <c r="AB63" s="8" t="inlineStr">
+      <c r="AB63" s="8" t="inlineStr"/>
+      <c r="AC63" s="8" t="inlineStr">
         <is>
           <t>VADN173</t>
         </is>
       </c>
-      <c r="AC63" s="8" t="inlineStr"/>
       <c r="AD63" s="8" t="inlineStr"/>
-      <c r="AE63" s="8" t="inlineStr">
+      <c r="AE63" s="8" t="inlineStr"/>
+      <c r="AF63" s="8" t="inlineStr">
         <is>
           <t>VADN173</t>
         </is>
       </c>
-      <c r="AF63" s="8" t="inlineStr"/>
       <c r="AG63" s="9" t="inlineStr"/>
     </row>
     <row r="64">
@@ -7664,11 +7812,7 @@
           <t>PAT_MED_24H</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
-        <is>
-          <t>VADN177</t>
-        </is>
-      </c>
+      <c r="C64" s="7" t="inlineStr"/>
       <c r="D64" s="8" t="inlineStr"/>
       <c r="E64" s="9" t="inlineStr"/>
       <c r="F64" s="9" t="inlineStr"/>
@@ -7751,22 +7895,18 @@
       <c r="W64" s="8" t="inlineStr"/>
       <c r="X64" s="8" t="inlineStr"/>
       <c r="Y64" s="8" t="inlineStr"/>
-      <c r="Z64" s="9" t="inlineStr"/>
-      <c r="AA64" s="9" t="inlineStr">
+      <c r="Z64" s="9" t="inlineStr">
         <is>
           <t>VADN177</t>
         </is>
       </c>
+      <c r="AA64" s="9" t="inlineStr"/>
       <c r="AB64" s="8" t="inlineStr"/>
       <c r="AC64" s="8" t="inlineStr"/>
       <c r="AD64" s="8" t="inlineStr"/>
       <c r="AE64" s="8" t="inlineStr"/>
       <c r="AF64" s="8" t="inlineStr"/>
-      <c r="AG64" s="9" t="inlineStr">
-        <is>
-          <t>VADN177</t>
-        </is>
-      </c>
+      <c r="AG64" s="9" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -7779,7 +7919,11 @@
           <t>PAT_MED_24H</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr"/>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>VADN177</t>
+        </is>
+      </c>
       <c r="D65" s="8" t="inlineStr"/>
       <c r="E65" s="9" t="inlineStr"/>
       <c r="F65" s="9" t="inlineStr"/>
@@ -7792,23 +7936,23 @@
       <c r="I65" s="8" t="inlineStr"/>
       <c r="J65" s="8" t="inlineStr"/>
       <c r="K65" s="8" t="inlineStr"/>
-      <c r="L65" s="9" t="inlineStr">
+      <c r="L65" s="9" t="inlineStr"/>
+      <c r="M65" s="9" t="inlineStr">
         <is>
           <t>VADN177</t>
         </is>
       </c>
-      <c r="M65" s="9" t="inlineStr"/>
       <c r="N65" s="8" t="inlineStr"/>
       <c r="O65" s="8" t="inlineStr"/>
       <c r="P65" s="8" t="inlineStr"/>
       <c r="Q65" s="8" t="inlineStr"/>
       <c r="R65" s="8" t="inlineStr"/>
-      <c r="S65" s="9" t="inlineStr"/>
-      <c r="T65" s="9" t="inlineStr">
+      <c r="S65" s="9" t="inlineStr">
         <is>
           <t>VADN177</t>
         </is>
       </c>
+      <c r="T65" s="9" t="inlineStr"/>
       <c r="U65" s="10" t="inlineStr">
         <is>
           <t>VAC</t>
@@ -7906,11 +8050,7 @@
       <c r="P66" s="8" t="inlineStr"/>
       <c r="Q66" s="8" t="inlineStr"/>
       <c r="R66" s="8" t="inlineStr"/>
-      <c r="S66" s="9" t="inlineStr">
-        <is>
-          <t>VADN177</t>
-        </is>
-      </c>
+      <c r="S66" s="9" t="inlineStr"/>
       <c r="T66" s="9" t="inlineStr"/>
       <c r="U66" s="8" t="inlineStr"/>
       <c r="V66" s="8" t="inlineStr"/>
@@ -7918,13 +8058,21 @@
       <c r="X66" s="8" t="inlineStr"/>
       <c r="Y66" s="8" t="inlineStr"/>
       <c r="Z66" s="9" t="inlineStr"/>
-      <c r="AA66" s="9" t="inlineStr"/>
+      <c r="AA66" s="9" t="inlineStr">
+        <is>
+          <t>VADN177</t>
+        </is>
+      </c>
       <c r="AB66" s="8" t="inlineStr"/>
       <c r="AC66" s="8" t="inlineStr"/>
       <c r="AD66" s="8" t="inlineStr"/>
       <c r="AE66" s="8" t="inlineStr"/>
       <c r="AF66" s="8" t="inlineStr"/>
-      <c r="AG66" s="9" t="inlineStr"/>
+      <c r="AG66" s="9" t="inlineStr">
+        <is>
+          <t>VADN177</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -7950,12 +8098,12 @@
       <c r="I67" s="8" t="inlineStr"/>
       <c r="J67" s="8" t="inlineStr"/>
       <c r="K67" s="8" t="inlineStr"/>
-      <c r="L67" s="9" t="inlineStr"/>
-      <c r="M67" s="9" t="inlineStr">
+      <c r="L67" s="9" t="inlineStr">
         <is>
           <t>VADN177</t>
         </is>
       </c>
+      <c r="M67" s="9" t="inlineStr"/>
       <c r="N67" s="8" t="inlineStr"/>
       <c r="O67" s="8" t="inlineStr"/>
       <c r="P67" s="8" t="inlineStr"/>
@@ -7968,11 +8116,7 @@
       <c r="W67" s="8" t="inlineStr"/>
       <c r="X67" s="8" t="inlineStr"/>
       <c r="Y67" s="8" t="inlineStr"/>
-      <c r="Z67" s="9" t="inlineStr">
-        <is>
-          <t>VADN177</t>
-        </is>
-      </c>
+      <c r="Z67" s="9" t="inlineStr"/>
       <c r="AA67" s="9" t="inlineStr"/>
       <c r="AB67" s="8" t="inlineStr"/>
       <c r="AC67" s="8" t="inlineStr"/>
@@ -7992,68 +8136,72 @@
           <t>PAT_VAL</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr"/>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>VADN002</t>
+          <t>VADN006</t>
         </is>
       </c>
       <c r="E68" s="9" t="inlineStr"/>
       <c r="F68" s="9" t="inlineStr"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="J68" s="8" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="K68" s="8" t="inlineStr">
+        <is>
           <t>VADN034</t>
         </is>
       </c>
-      <c r="H68" s="7" t="inlineStr"/>
-      <c r="I68" s="8" t="inlineStr"/>
-      <c r="J68" s="8" t="inlineStr">
+      <c r="L68" s="9" t="inlineStr"/>
+      <c r="M68" s="9" t="inlineStr"/>
+      <c r="N68" s="8" t="inlineStr"/>
+      <c r="O68" s="8" t="inlineStr"/>
+      <c r="P68" s="8" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="Q68" s="8" t="inlineStr">
         <is>
           <t>VADN152</t>
         </is>
       </c>
-      <c r="K68" s="8" t="inlineStr">
+      <c r="R68" s="8" t="inlineStr">
+        <is>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="S68" s="9" t="inlineStr">
         <is>
           <t>VADN034</t>
         </is>
       </c>
-      <c r="L68" s="9" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
-      <c r="M68" s="9" t="inlineStr"/>
-      <c r="N68" s="8" t="inlineStr">
-        <is>
-          <t>VADN004</t>
-        </is>
-      </c>
-      <c r="O68" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="P68" s="8" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="Q68" s="8" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="R68" s="8" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="S68" s="9" t="inlineStr">
-        <is>
-          <t>VADN038</t>
-        </is>
-      </c>
-      <c r="T68" s="9" t="inlineStr"/>
+      <c r="T68" s="9" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
       <c r="U68" s="10" t="inlineStr">
         <is>
           <t>VAC</t>
@@ -8131,107 +8279,115 @@
           <t>PAT_VAL</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr"/>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>VADN004</t>
+        </is>
+      </c>
       <c r="D69" s="8" t="inlineStr"/>
-      <c r="E69" s="9" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr"/>
+      <c r="F69" s="9" t="inlineStr"/>
+      <c r="G69" s="8" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>VADN026</t>
+        </is>
+      </c>
+      <c r="I69" s="8" t="inlineStr"/>
+      <c r="J69" s="8" t="inlineStr"/>
+      <c r="K69" s="8" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="L69" s="9" t="inlineStr">
+        <is>
+          <t>VADN027</t>
+        </is>
+      </c>
+      <c r="M69" s="9" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="N69" s="8" t="inlineStr"/>
+      <c r="O69" s="8" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="P69" s="8" t="inlineStr"/>
+      <c r="Q69" s="8" t="inlineStr"/>
+      <c r="R69" s="8" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="S69" s="9" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="T69" s="9" t="inlineStr"/>
+      <c r="U69" s="8" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="V69" s="8" t="inlineStr">
         <is>
           <t>VADN031</t>
         </is>
       </c>
-      <c r="F69" s="9" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="8" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="J69" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="K69" s="8" t="inlineStr"/>
-      <c r="L69" s="9" t="inlineStr">
+      <c r="W69" s="8" t="inlineStr">
+        <is>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="X69" s="8" t="inlineStr">
         <is>
           <t>VADN034</t>
         </is>
       </c>
-      <c r="M69" s="9" t="inlineStr"/>
-      <c r="N69" s="8" t="inlineStr"/>
-      <c r="O69" s="8" t="inlineStr"/>
-      <c r="P69" s="8" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="Q69" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="R69" s="8" t="inlineStr"/>
-      <c r="S69" s="9" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="T69" s="9" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="U69" s="8" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
-      <c r="V69" s="8" t="inlineStr"/>
-      <c r="W69" s="8" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="X69" s="8" t="inlineStr">
+      <c r="Y69" s="8" t="inlineStr">
         <is>
           <t>VADN029</t>
-        </is>
-      </c>
-      <c r="Y69" s="8" t="inlineStr">
-        <is>
-          <t>VADN032</t>
         </is>
       </c>
       <c r="Z69" s="9" t="inlineStr"/>
       <c r="AA69" s="9" t="inlineStr"/>
       <c r="AB69" s="8" t="inlineStr">
         <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="AC69" s="8" t="inlineStr"/>
-      <c r="AD69" s="8" t="inlineStr"/>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="AC69" s="8" t="inlineStr">
+        <is>
+          <t>VADN004</t>
+        </is>
+      </c>
+      <c r="AD69" s="8" t="inlineStr">
+        <is>
+          <t>VADN040</t>
+        </is>
+      </c>
       <c r="AE69" s="8" t="inlineStr">
         <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="AF69" s="8" t="inlineStr">
+        <is>
           <t>VADN034</t>
         </is>
       </c>
-      <c r="AF69" s="8" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
       <c r="AG69" s="9" t="inlineStr">
         <is>
-          <t>VADN034</t>
+          <t>VADN029</t>
         </is>
       </c>
     </row>
@@ -8247,104 +8403,116 @@
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr"/>
-      <c r="D70" s="8" t="inlineStr"/>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>VADN004</t>
+        </is>
+      </c>
       <c r="E70" s="9" t="inlineStr">
         <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="F70" s="9" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
+          <t>VADN038</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="inlineStr"/>
       <c r="G70" s="8" t="inlineStr"/>
       <c r="H70" s="7" t="inlineStr">
         <is>
+          <t>VADN038</t>
+        </is>
+      </c>
+      <c r="I70" s="8" t="inlineStr"/>
+      <c r="J70" s="8" t="inlineStr"/>
+      <c r="K70" s="8" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="L70" s="9" t="inlineStr">
+        <is>
           <t>VADN026</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr"/>
-      <c r="J70" s="8" t="inlineStr">
+      <c r="M70" s="9" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="N70" s="8" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="O70" s="8" t="inlineStr">
         <is>
           <t>VADN004</t>
         </is>
       </c>
-      <c r="K70" s="8" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="L70" s="9" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="M70" s="9" t="inlineStr"/>
-      <c r="N70" s="8" t="inlineStr"/>
-      <c r="O70" s="8" t="inlineStr">
+      <c r="P70" s="8" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="Q70" s="8" t="inlineStr"/>
+      <c r="R70" s="8" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="S70" s="9" t="inlineStr"/>
+      <c r="T70" s="9" t="inlineStr"/>
+      <c r="U70" s="8" t="inlineStr">
+        <is>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="V70" s="8" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="W70" s="8" t="inlineStr"/>
+      <c r="X70" s="8" t="inlineStr"/>
+      <c r="Y70" s="8" t="inlineStr">
         <is>
           <t>VADN006</t>
         </is>
       </c>
-      <c r="P70" s="8" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="Q70" s="8" t="inlineStr">
-        <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="R70" s="8" t="inlineStr"/>
-      <c r="S70" s="9" t="inlineStr"/>
-      <c r="T70" s="9" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="U70" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="V70" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="W70" s="8" t="inlineStr"/>
-      <c r="X70" s="8" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="Y70" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="Z70" s="9" t="inlineStr"/>
+      <c r="Z70" s="9" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
       <c r="AA70" s="9" t="inlineStr"/>
       <c r="AB70" s="8" t="inlineStr">
         <is>
-          <t>VADN052</t>
+          <t>VADN003</t>
         </is>
       </c>
       <c r="AC70" s="8" t="inlineStr">
         <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="AD70" s="8" t="inlineStr"/>
-      <c r="AE70" s="8" t="inlineStr"/>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="AD70" s="8" t="inlineStr">
+        <is>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="AE70" s="8" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
       <c r="AF70" s="8" t="inlineStr">
         <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="AG70" s="9" t="inlineStr"/>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="AG70" s="9" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -8357,103 +8525,103 @@
           <t>PAT_VAL</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr"/>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
-      <c r="E71" s="9" t="inlineStr"/>
-      <c r="F71" s="9" t="inlineStr"/>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="inlineStr"/>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>VADN040</t>
+        </is>
+      </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="H71" s="7" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="8" t="inlineStr">
         <is>
           <t>VADN051</t>
         </is>
       </c>
-      <c r="J71" s="8" t="inlineStr"/>
+      <c r="J71" s="8" t="inlineStr">
+        <is>
+          <t>VADN051</t>
+        </is>
+      </c>
       <c r="K71" s="8" t="inlineStr"/>
-      <c r="L71" s="9" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
+      <c r="L71" s="9" t="inlineStr"/>
       <c r="M71" s="9" t="inlineStr"/>
       <c r="N71" s="8" t="inlineStr">
         <is>
           <t>VADN031</t>
         </is>
       </c>
-      <c r="O71" s="8" t="inlineStr"/>
-      <c r="P71" s="8" t="inlineStr">
+      <c r="O71" s="8" t="inlineStr">
         <is>
           <t>VADN040</t>
         </is>
       </c>
-      <c r="Q71" s="8" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="R71" s="8" t="inlineStr"/>
-      <c r="S71" s="9" t="inlineStr"/>
+      <c r="P71" s="8" t="inlineStr"/>
+      <c r="Q71" s="8" t="inlineStr"/>
+      <c r="R71" s="8" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="S71" s="9" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
       <c r="T71" s="9" t="inlineStr"/>
       <c r="U71" s="8" t="inlineStr">
         <is>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="V71" s="8" t="inlineStr">
+        <is>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="W71" s="8" t="inlineStr">
+        <is>
           <t>VADN040</t>
         </is>
       </c>
-      <c r="V71" s="8" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
-      <c r="W71" s="8" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
-      <c r="X71" s="8" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
+      <c r="X71" s="8" t="inlineStr"/>
       <c r="Y71" s="8" t="inlineStr"/>
       <c r="Z71" s="9" t="inlineStr">
         <is>
-          <t>VADN052</t>
+          <t>VADN029</t>
         </is>
       </c>
       <c r="AA71" s="9" t="inlineStr"/>
-      <c r="AB71" s="8" t="inlineStr"/>
+      <c r="AB71" s="8" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
       <c r="AC71" s="8" t="inlineStr"/>
       <c r="AD71" s="8" t="inlineStr">
         <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="AE71" s="8" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="AF71" s="8" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="AE71" s="8" t="inlineStr"/>
+      <c r="AF71" s="8" t="inlineStr"/>
       <c r="AG71" s="9" t="inlineStr">
         <is>
-          <t>VADN027</t>
+          <t>VADN052</t>
         </is>
       </c>
     </row>
@@ -8470,38 +8638,38 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>VADN006</t>
+          <t>VADN025</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="E72" s="9" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr"/>
       <c r="F72" s="9" t="inlineStr"/>
-      <c r="G72" s="8" t="inlineStr"/>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>VADN029</t>
+        </is>
+      </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>VADN038</t>
+          <t>VADN030</t>
         </is>
       </c>
       <c r="I72" s="8" t="inlineStr"/>
-      <c r="J72" s="8" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
+      <c r="J72" s="8" t="inlineStr"/>
       <c r="K72" s="8" t="inlineStr">
         <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="L72" s="9" t="inlineStr"/>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="L72" s="9" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
       <c r="M72" s="9" t="inlineStr"/>
       <c r="N72" s="8" t="inlineStr">
         <is>
@@ -8510,64 +8678,64 @@
       </c>
       <c r="O72" s="8" t="inlineStr">
         <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="P72" s="8" t="inlineStr"/>
+      <c r="Q72" s="8" t="inlineStr"/>
+      <c r="R72" s="8" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="S72" s="9" t="inlineStr">
+        <is>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="T72" s="9" t="inlineStr"/>
+      <c r="U72" s="8" t="inlineStr">
+        <is>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="V72" s="8" t="inlineStr"/>
+      <c r="W72" s="8" t="inlineStr"/>
+      <c r="X72" s="8" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="Y72" s="8" t="inlineStr">
+        <is>
           <t>VADN034</t>
         </is>
       </c>
-      <c r="P72" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="Q72" s="8" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="R72" s="8" t="inlineStr"/>
-      <c r="S72" s="9" t="inlineStr">
-        <is>
-          <t>VADN027</t>
-        </is>
-      </c>
-      <c r="T72" s="9" t="inlineStr"/>
-      <c r="U72" s="8" t="inlineStr"/>
-      <c r="V72" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="W72" s="8" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="X72" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="Y72" s="8" t="inlineStr"/>
       <c r="Z72" s="9" t="inlineStr">
         <is>
-          <t>VADN001</t>
+          <t>VADN038</t>
         </is>
       </c>
       <c r="AA72" s="9" t="inlineStr"/>
-      <c r="AB72" s="8" t="inlineStr"/>
-      <c r="AC72" s="8" t="inlineStr"/>
-      <c r="AD72" s="8" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
+      <c r="AB72" s="8" t="inlineStr">
+        <is>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="AC72" s="8" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="AD72" s="8" t="inlineStr"/>
       <c r="AE72" s="8" t="inlineStr">
         <is>
-          <t>VADN022</t>
+          <t>VADN028</t>
         </is>
       </c>
       <c r="AF72" s="8" t="inlineStr">
         <is>
-          <t>VADN034</t>
+          <t>VADN032</t>
         </is>
       </c>
       <c r="AG72" s="9" t="inlineStr">
@@ -8587,113 +8755,113 @@
           <t>PAT_VAL</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr"/>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="E73" s="9" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="F73" s="9" t="inlineStr"/>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="7" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr">
+        <is>
+          <t>VADN004</t>
+        </is>
+      </c>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="K73" s="8" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="L73" s="9" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="M73" s="9" t="inlineStr"/>
+      <c r="N73" s="8" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="O73" s="8" t="inlineStr"/>
+      <c r="P73" s="8" t="inlineStr"/>
+      <c r="Q73" s="8" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="R73" s="8" t="inlineStr">
+        <is>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="S73" s="9" t="inlineStr">
         <is>
           <t>VADN030</t>
         </is>
       </c>
-      <c r="D73" s="8" t="inlineStr"/>
-      <c r="E73" s="9" t="inlineStr"/>
-      <c r="F73" s="9" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="G73" s="8" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="H73" s="7" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
-      <c r="J73" s="8" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="K73" s="8" t="inlineStr"/>
-      <c r="L73" s="9" t="inlineStr"/>
-      <c r="M73" s="9" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="N73" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="O73" s="8" t="inlineStr"/>
-      <c r="P73" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="Q73" s="8" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="R73" s="8" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="S73" s="9" t="inlineStr"/>
       <c r="T73" s="9" t="inlineStr"/>
       <c r="U73" s="8" t="inlineStr">
         <is>
-          <t>VADN022</t>
+          <t>VADN025</t>
         </is>
       </c>
       <c r="V73" s="8" t="inlineStr">
         <is>
-          <t>VADN040</t>
+          <t>VADN025</t>
         </is>
       </c>
       <c r="W73" s="8" t="inlineStr"/>
       <c r="X73" s="8" t="inlineStr"/>
       <c r="Y73" s="8" t="inlineStr">
         <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="Z73" s="9" t="inlineStr">
+        <is>
           <t>VADN034</t>
         </is>
       </c>
-      <c r="Z73" s="9" t="inlineStr">
+      <c r="AA73" s="9" t="inlineStr"/>
+      <c r="AB73" s="8" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="AC73" s="8" t="inlineStr">
         <is>
           <t>VADN034</t>
         </is>
       </c>
-      <c r="AA73" s="9" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="AB73" s="8" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="AC73" s="8" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
       <c r="AD73" s="8" t="inlineStr"/>
-      <c r="AE73" s="8" t="inlineStr"/>
+      <c r="AE73" s="8" t="inlineStr">
+        <is>
+          <t>VADN004</t>
+        </is>
+      </c>
       <c r="AF73" s="8" t="inlineStr">
         <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="AG73" s="9" t="inlineStr"/>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="AG73" s="9" t="inlineStr">
+        <is>
+          <t>VADN051</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -8708,109 +8876,109 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>VADN001</t>
+          <t>VADN003</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>VADN004</t>
+          <t>VADN152</t>
         </is>
       </c>
       <c r="E74" s="9" t="inlineStr"/>
       <c r="F74" s="9" t="inlineStr"/>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="8" t="inlineStr"/>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
       <c r="J74" s="8" t="inlineStr"/>
-      <c r="K74" s="8" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
+      <c r="K74" s="8" t="inlineStr"/>
       <c r="L74" s="9" t="inlineStr">
         <is>
-          <t>VADN022</t>
+          <t>VADN152</t>
         </is>
       </c>
       <c r="M74" s="9" t="inlineStr"/>
-      <c r="N74" s="8" t="inlineStr">
+      <c r="N74" s="8" t="inlineStr"/>
+      <c r="O74" s="8" t="inlineStr"/>
+      <c r="P74" s="8" t="inlineStr">
+        <is>
+          <t>VADN004</t>
+        </is>
+      </c>
+      <c r="Q74" s="8" t="inlineStr">
+        <is>
+          <t>VADN004</t>
+        </is>
+      </c>
+      <c r="R74" s="8" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="S74" s="9" t="inlineStr">
+        <is>
+          <t>VADN038</t>
+        </is>
+      </c>
+      <c r="T74" s="9" t="inlineStr"/>
+      <c r="U74" s="8" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="V74" s="8" t="inlineStr"/>
+      <c r="W74" s="8" t="inlineStr"/>
+      <c r="X74" s="8" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="Y74" s="8" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="Z74" s="9" t="inlineStr">
+        <is>
+          <t>VADN026</t>
+        </is>
+      </c>
+      <c r="AA74" s="9" t="inlineStr"/>
+      <c r="AB74" s="8" t="inlineStr">
         <is>
           <t>VADN032</t>
         </is>
       </c>
-      <c r="O74" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="P74" s="8" t="inlineStr"/>
-      <c r="Q74" s="8" t="inlineStr"/>
-      <c r="R74" s="8" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="S74" s="9" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="T74" s="9" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="U74" s="8" t="inlineStr">
+      <c r="AC74" s="8" t="inlineStr">
         <is>
           <t>VADN030</t>
         </is>
       </c>
-      <c r="V74" s="8" t="inlineStr">
-        <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="W74" s="8" t="inlineStr"/>
-      <c r="X74" s="8" t="inlineStr"/>
-      <c r="Y74" s="8" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="Z74" s="9" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="AA74" s="9" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="AB74" s="8" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="AC74" s="8" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="AD74" s="8" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="AE74" s="8" t="inlineStr"/>
-      <c r="AF74" s="8" t="inlineStr"/>
+      <c r="AD74" s="8" t="inlineStr"/>
+      <c r="AE74" s="8" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="AF74" s="8" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
       <c r="AG74" s="9" t="inlineStr">
         <is>
-          <t>VADN025</t>
+          <t>VADN028</t>
         </is>
       </c>
     </row>
@@ -8827,110 +8995,114 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="inlineStr"/>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="I75" s="8" t="inlineStr"/>
+      <c r="J75" s="8" t="inlineStr"/>
+      <c r="K75" s="8" t="inlineStr">
+        <is>
           <t>VADN003</t>
         </is>
       </c>
-      <c r="D75" s="8" t="inlineStr">
+      <c r="L75" s="9" t="inlineStr">
+        <is>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="M75" s="9" t="inlineStr"/>
+      <c r="N75" s="8" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="O75" s="8" t="inlineStr"/>
+      <c r="P75" s="8" t="inlineStr"/>
+      <c r="Q75" s="8" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="R75" s="8" t="inlineStr">
         <is>
           <t>VADN006</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr">
-        <is>
-          <t>VADN038</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="inlineStr"/>
-      <c r="G75" s="8" t="inlineStr"/>
-      <c r="H75" s="7" t="inlineStr"/>
-      <c r="I75" s="8" t="inlineStr">
+      <c r="S75" s="9" t="inlineStr">
+        <is>
+          <t>VADN026</t>
+        </is>
+      </c>
+      <c r="T75" s="9" t="inlineStr">
         <is>
           <t>VADN005</t>
         </is>
       </c>
-      <c r="J75" s="8" t="inlineStr">
+      <c r="U75" s="8" t="inlineStr">
         <is>
           <t>VADN028</t>
         </is>
       </c>
-      <c r="K75" s="8" t="inlineStr"/>
-      <c r="L75" s="9" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="M75" s="9" t="inlineStr">
+      <c r="V75" s="8" t="inlineStr"/>
+      <c r="W75" s="8" t="inlineStr"/>
+      <c r="X75" s="8" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="Y75" s="8" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="Z75" s="9" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="AA75" s="9" t="inlineStr"/>
+      <c r="AB75" s="8" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="AC75" s="8" t="inlineStr">
+        <is>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="AD75" s="8" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="AE75" s="8" t="inlineStr"/>
+      <c r="AF75" s="8" t="inlineStr">
         <is>
           <t>VADN005</t>
         </is>
       </c>
-      <c r="N75" s="8" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="O75" s="8" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="P75" s="8" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
-      <c r="Q75" s="8" t="inlineStr"/>
-      <c r="R75" s="8" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
-      <c r="S75" s="9" t="inlineStr"/>
-      <c r="T75" s="9" t="inlineStr"/>
-      <c r="U75" s="8" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="V75" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="W75" s="8" t="inlineStr">
-        <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="X75" s="8" t="inlineStr"/>
-      <c r="Y75" s="8" t="inlineStr"/>
-      <c r="Z75" s="9" t="inlineStr"/>
-      <c r="AA75" s="9" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="AB75" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="AC75" s="8" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
-      <c r="AD75" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="AE75" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="AF75" s="8" t="inlineStr"/>
       <c r="AG75" s="9" t="inlineStr"/>
     </row>
     <row r="76">
@@ -8948,109 +9120,101 @@
       <c r="D76" s="8" t="inlineStr"/>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="inlineStr">
+          <t>VADN027</t>
+        </is>
+      </c>
+      <c r="F76" s="9" t="inlineStr"/>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr"/>
+      <c r="I76" s="8" t="inlineStr"/>
+      <c r="J76" s="8" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="K76" s="8" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="L76" s="9" t="inlineStr">
         <is>
           <t>VADN051</t>
-        </is>
-      </c>
-      <c r="G76" s="8" t="inlineStr"/>
-      <c r="H76" s="7" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
-      <c r="I76" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="J76" s="8" t="inlineStr"/>
-      <c r="K76" s="8" t="inlineStr"/>
-      <c r="L76" s="9" t="inlineStr">
-        <is>
-          <t>VADN027</t>
         </is>
       </c>
       <c r="M76" s="9" t="inlineStr"/>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>VADN051</t>
+          <t>VADN040</t>
         </is>
       </c>
       <c r="O76" s="8" t="inlineStr"/>
       <c r="P76" s="8" t="inlineStr">
         <is>
-          <t>VADN004</t>
+          <t>VADN152</t>
         </is>
       </c>
       <c r="Q76" s="8" t="inlineStr">
         <is>
-          <t>VADN001</t>
+          <t>VADN005</t>
         </is>
       </c>
       <c r="R76" s="8" t="inlineStr">
         <is>
-          <t>VADN022</t>
+          <t>VADN152</t>
         </is>
       </c>
       <c r="S76" s="9" t="inlineStr"/>
       <c r="T76" s="9" t="inlineStr"/>
       <c r="U76" s="8" t="inlineStr">
         <is>
-          <t>VADN001</t>
+          <t>VADN029</t>
         </is>
       </c>
       <c r="V76" s="8" t="inlineStr">
         <is>
-          <t>VADN004</t>
-        </is>
-      </c>
-      <c r="W76" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="W76" s="8" t="inlineStr"/>
       <c r="X76" s="8" t="inlineStr">
         <is>
-          <t>VADN025</t>
+          <t>VADN030</t>
         </is>
       </c>
       <c r="Y76" s="8" t="inlineStr">
         <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="Z76" s="9" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="Z76" s="9" t="inlineStr"/>
       <c r="AA76" s="9" t="inlineStr"/>
-      <c r="AB76" s="8" t="inlineStr"/>
+      <c r="AB76" s="8" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
       <c r="AC76" s="8" t="inlineStr"/>
       <c r="AD76" s="8" t="inlineStr">
         <is>
-          <t>VADN025</t>
+          <t>VADN002</t>
         </is>
       </c>
       <c r="AE76" s="8" t="inlineStr">
         <is>
-          <t>VADN001</t>
+          <t>VADN002</t>
         </is>
       </c>
       <c r="AF76" s="8" t="inlineStr">
         <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="AG76" s="9" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="AG76" s="9" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -9065,114 +9229,114 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>VADN031</t>
+          <t>VADN005</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>VADN030</t>
+          <t>VADN003</t>
         </is>
       </c>
       <c r="E77" s="9" t="inlineStr">
         <is>
-          <t>VADN030</t>
+          <t>VADN052</t>
         </is>
       </c>
       <c r="F77" s="9" t="inlineStr"/>
       <c r="G77" s="8" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
+      <c r="H77" s="7" t="inlineStr"/>
       <c r="I77" s="8" t="inlineStr">
         <is>
-          <t>VADN003</t>
+          <t>VADN001</t>
         </is>
       </c>
       <c r="J77" s="8" t="inlineStr">
         <is>
+          <t>VADN004</t>
+        </is>
+      </c>
+      <c r="K77" s="8" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="L77" s="9" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="M77" s="9" t="inlineStr">
+        <is>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="N77" s="8" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="O77" s="8" t="inlineStr"/>
+      <c r="P77" s="8" t="inlineStr"/>
+      <c r="Q77" s="8" t="inlineStr">
+        <is>
           <t>VADN001</t>
         </is>
       </c>
-      <c r="K77" s="8" t="inlineStr">
-        <is>
-          <t>VADN004</t>
-        </is>
-      </c>
-      <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="9" t="inlineStr"/>
-      <c r="N77" s="8" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="O77" s="8" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="P77" s="8" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="Q77" s="8" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
       <c r="R77" s="8" t="inlineStr">
         <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="S77" s="9" t="inlineStr"/>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="S77" s="9" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
       <c r="T77" s="9" t="inlineStr"/>
       <c r="U77" s="8" t="inlineStr">
         <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="V77" s="8" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="W77" s="8" t="inlineStr"/>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="V77" s="8" t="inlineStr"/>
+      <c r="W77" s="8" t="inlineStr">
+        <is>
+          <t>VADN004</t>
+        </is>
+      </c>
       <c r="X77" s="8" t="inlineStr">
         <is>
-          <t>VADN003</t>
+          <t>VADN006</t>
         </is>
       </c>
       <c r="Y77" s="8" t="inlineStr">
         <is>
-          <t>VADN025</t>
+          <t>VADN004</t>
         </is>
       </c>
       <c r="Z77" s="9" t="inlineStr"/>
       <c r="AA77" s="9" t="inlineStr"/>
       <c r="AB77" s="8" t="inlineStr">
         <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="AC77" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="AC77" s="8" t="inlineStr"/>
       <c r="AD77" s="8" t="inlineStr">
         <is>
-          <t>VADN032</t>
+          <t>VADN003</t>
         </is>
       </c>
       <c r="AE77" s="8" t="inlineStr">
         <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="AF77" s="8" t="inlineStr"/>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="AF77" s="8" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
       <c r="AG77" s="9" t="inlineStr"/>
     </row>
     <row r="78">
@@ -9188,115 +9352,115 @@
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>VADN032</t>
+          <t>VADN026</t>
         </is>
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="E78" s="9" t="inlineStr">
-        <is>
-          <t>VADN027</t>
-        </is>
-      </c>
-      <c r="F78" s="9" t="inlineStr"/>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="inlineStr"/>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
       <c r="G78" s="8" t="inlineStr"/>
-      <c r="H78" s="7" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
+      <c r="H78" s="7" t="inlineStr"/>
       <c r="I78" s="8" t="inlineStr">
         <is>
-          <t>VADN152</t>
+          <t>VADN002</t>
         </is>
       </c>
       <c r="J78" s="8" t="inlineStr">
         <is>
-          <t>VADN005</t>
+          <t>VADN029</t>
         </is>
       </c>
       <c r="K78" s="8" t="inlineStr">
         <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="L78" s="9" t="inlineStr"/>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="L78" s="9" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
       <c r="M78" s="9" t="inlineStr"/>
       <c r="N78" s="8" t="inlineStr">
         <is>
-          <t>VADN005</t>
+          <t>VADN029</t>
         </is>
       </c>
       <c r="O78" s="8" t="inlineStr">
         <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="P78" s="8" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
-      <c r="Q78" s="8" t="inlineStr"/>
-      <c r="R78" s="8" t="inlineStr"/>
-      <c r="S78" s="9" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="T78" s="9" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="P78" s="8" t="inlineStr"/>
+      <c r="Q78" s="8" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="R78" s="8" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="S78" s="9" t="inlineStr"/>
+      <c r="T78" s="9" t="inlineStr"/>
       <c r="U78" s="8" t="inlineStr">
         <is>
-          <t>VADN003</t>
+          <t>VADN004</t>
         </is>
       </c>
       <c r="V78" s="8" t="inlineStr">
         <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="W78" s="8" t="inlineStr"/>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="W78" s="8" t="inlineStr">
+        <is>
+          <t>VADN029</t>
+        </is>
+      </c>
       <c r="X78" s="8" t="inlineStr">
         <is>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="Y78" s="8" t="inlineStr">
+        <is>
           <t>VADN032</t>
-        </is>
-      </c>
-      <c r="Y78" s="8" t="inlineStr">
-        <is>
-          <t>VADN028</t>
         </is>
       </c>
       <c r="Z78" s="9" t="inlineStr"/>
       <c r="AA78" s="9" t="inlineStr"/>
       <c r="AB78" s="8" t="inlineStr">
         <is>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="AC78" s="8" t="inlineStr"/>
+      <c r="AD78" s="8" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="AE78" s="8" t="inlineStr">
+        <is>
           <t>VADN040</t>
         </is>
       </c>
-      <c r="AC78" s="8" t="inlineStr">
+      <c r="AF78" s="8" t="inlineStr">
         <is>
           <t>VADN051</t>
         </is>
       </c>
-      <c r="AD78" s="8" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="AE78" s="8" t="inlineStr"/>
-      <c r="AF78" s="8" t="inlineStr"/>
-      <c r="AG78" s="9" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
+      <c r="AG78" s="9" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
@@ -9310,104 +9474,112 @@
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr"/>
-      <c r="D79" s="8" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
+      <c r="D79" s="8" t="inlineStr"/>
       <c r="E79" s="9" t="inlineStr"/>
       <c r="F79" s="9" t="inlineStr"/>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>VADN025</t>
+          <t>VADN031</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="I79" s="8" t="inlineStr">
+        <is>
           <t>VADN028</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr"/>
-      <c r="J79" s="8" t="inlineStr"/>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
       <c r="K79" s="8" t="inlineStr">
         <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="L79" s="9" t="inlineStr">
-        <is>
-          <t>VADN038</t>
-        </is>
-      </c>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="L79" s="9" t="inlineStr"/>
       <c r="M79" s="9" t="inlineStr"/>
       <c r="N79" s="8" t="inlineStr">
         <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="O79" s="8" t="inlineStr">
+        <is>
           <t>VADN029</t>
         </is>
       </c>
-      <c r="O79" s="8" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
       <c r="P79" s="8" t="inlineStr">
         <is>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="Q79" s="8" t="inlineStr">
+        <is>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="R79" s="8" t="inlineStr">
+        <is>
           <t>VADN028</t>
         </is>
       </c>
-      <c r="Q79" s="8" t="inlineStr"/>
-      <c r="R79" s="8" t="inlineStr">
-        <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="S79" s="9" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
+      <c r="S79" s="9" t="inlineStr"/>
       <c r="T79" s="9" t="inlineStr"/>
       <c r="U79" s="8" t="inlineStr"/>
-      <c r="V79" s="8" t="inlineStr"/>
+      <c r="V79" s="8" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
       <c r="W79" s="8" t="inlineStr">
         <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="X79" s="8" t="inlineStr">
+        <is>
+          <t>VADN004</t>
+        </is>
+      </c>
+      <c r="Y79" s="8" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="Z79" s="9" t="inlineStr"/>
+      <c r="AA79" s="9" t="inlineStr"/>
+      <c r="AB79" s="8" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="AC79" s="8" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="AD79" s="8" t="inlineStr"/>
+      <c r="AE79" s="8" t="inlineStr">
+        <is>
           <t>VADN030</t>
         </is>
       </c>
-      <c r="X79" s="8" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
-      <c r="Y79" s="8" t="inlineStr"/>
-      <c r="Z79" s="9" t="inlineStr">
+      <c r="AF79" s="8" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="AG79" s="9" t="inlineStr">
         <is>
           <t>VADN026</t>
         </is>
       </c>
-      <c r="AA79" s="9" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="AB79" s="8" t="inlineStr"/>
-      <c r="AC79" s="8" t="inlineStr"/>
-      <c r="AD79" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="AE79" s="8" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="AF79" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="AG79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -9422,7 +9594,7 @@
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>VADN029</t>
+          <t>VADN027</t>
         </is>
       </c>
       <c r="D80" s="8" t="inlineStr">
@@ -9432,7 +9604,7 @@
       </c>
       <c r="E80" s="9" t="inlineStr">
         <is>
-          <t>VADN051</t>
+          <t>VADN026</t>
         </is>
       </c>
       <c r="F80" s="9" t="inlineStr"/>
@@ -9514,49 +9686,53 @@
       <c r="V80" s="8" t="inlineStr"/>
       <c r="W80" s="8" t="inlineStr">
         <is>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="X80" s="8" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="Y80" s="8" t="inlineStr">
+        <is>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="Z80" s="9" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="AA80" s="9" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="AB80" s="8" t="inlineStr"/>
+      <c r="AC80" s="8" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="AD80" s="8" t="inlineStr">
+        <is>
           <t>VADN006</t>
         </is>
       </c>
-      <c r="X80" s="8" t="inlineStr">
-        <is>
-          <t>VADN004</t>
-        </is>
-      </c>
-      <c r="Y80" s="8" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
-      <c r="Z80" s="9" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="AA80" s="9" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="AB80" s="8" t="inlineStr"/>
-      <c r="AC80" s="8" t="inlineStr"/>
-      <c r="AD80" s="8" t="inlineStr">
-        <is>
-          <t>VADN004</t>
-        </is>
-      </c>
       <c r="AE80" s="8" t="inlineStr">
         <is>
-          <t>VADN004</t>
+          <t>VADN005</t>
         </is>
       </c>
       <c r="AF80" s="8" t="inlineStr">
         <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="AG80" s="9" t="inlineStr">
+        <is>
           <t>VADN001</t>
-        </is>
-      </c>
-      <c r="AG80" s="9" t="inlineStr">
-        <is>
-          <t>VADN002</t>
         </is>
       </c>
     </row>
@@ -9573,66 +9749,70 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr"/>
+      <c r="F81" s="9" t="inlineStr"/>
+      <c r="G81" s="8" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="H81" s="7" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="K81" s="8" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="L81" s="9" t="inlineStr"/>
+      <c r="M81" s="9" t="inlineStr"/>
+      <c r="N81" s="8" t="inlineStr">
+        <is>
           <t>VADN005</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="E81" s="9" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="F81" s="9" t="inlineStr"/>
-      <c r="G81" s="8" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
-      <c r="I81" s="8" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
-      <c r="J81" s="8" t="inlineStr">
+      <c r="O81" s="8" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="P81" s="8" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="Q81" s="8" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="R81" s="8" t="inlineStr">
         <is>
           <t>VADN030</t>
         </is>
       </c>
-      <c r="K81" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="L81" s="9" t="inlineStr"/>
-      <c r="M81" s="9" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="N81" s="8" t="inlineStr"/>
-      <c r="O81" s="8" t="inlineStr"/>
-      <c r="P81" s="8" t="inlineStr"/>
-      <c r="Q81" s="8" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="R81" s="8" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
-      <c r="S81" s="9" t="inlineStr">
-        <is>
-          <t>VADN026</t>
-        </is>
-      </c>
-      <c r="T81" s="9" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
+      <c r="S81" s="9" t="inlineStr"/>
+      <c r="T81" s="9" t="inlineStr"/>
       <c r="U81" s="10" t="inlineStr">
         <is>
           <t>VAC</t>
@@ -9710,117 +9890,113 @@
           <t>PAT_VAL</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
+      <c r="C82" s="7" t="inlineStr"/>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="E82" s="9" t="inlineStr"/>
-      <c r="F82" s="9" t="inlineStr"/>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
       <c r="G82" s="8" t="inlineStr">
         <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="H82" s="7" t="inlineStr"/>
       <c r="I82" s="8" t="inlineStr">
         <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="J82" s="8" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
-      <c r="K82" s="8" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="L82" s="9" t="inlineStr"/>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="J82" s="8" t="inlineStr"/>
+      <c r="K82" s="8" t="inlineStr"/>
+      <c r="L82" s="9" t="inlineStr">
+        <is>
+          <t>VADN038</t>
+        </is>
+      </c>
       <c r="M82" s="9" t="inlineStr"/>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="O82" s="8" t="inlineStr"/>
-      <c r="P82" s="8" t="inlineStr"/>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="O82" s="8" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="P82" s="8" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
       <c r="Q82" s="8" t="inlineStr">
         <is>
-          <t>VADN004</t>
+          <t>VADN002</t>
         </is>
       </c>
       <c r="R82" s="8" t="inlineStr">
         <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="S82" s="9" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="S82" s="9" t="inlineStr"/>
       <c r="T82" s="9" t="inlineStr"/>
       <c r="U82" s="8" t="inlineStr">
         <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="V82" s="8" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="W82" s="8" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="X82" s="8" t="inlineStr"/>
+      <c r="Y82" s="8" t="inlineStr"/>
+      <c r="Z82" s="9" t="inlineStr">
+        <is>
           <t>VADN006</t>
         </is>
       </c>
-      <c r="V82" s="8" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="W82" s="8" t="inlineStr"/>
-      <c r="X82" s="8" t="inlineStr"/>
-      <c r="Y82" s="8" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="Z82" s="9" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="AA82" s="9" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
+      <c r="AA82" s="9" t="inlineStr"/>
       <c r="AB82" s="8" t="inlineStr">
         <is>
-          <t>VADN034</t>
+          <t>VADN004</t>
         </is>
       </c>
       <c r="AC82" s="8" t="inlineStr">
         <is>
-          <t>VADN028</t>
+          <t>VADN022</t>
         </is>
       </c>
       <c r="AD82" s="8" t="inlineStr">
         <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="AE82" s="8" t="inlineStr"/>
+          <t>VADN004</t>
+        </is>
+      </c>
+      <c r="AE82" s="8" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
       <c r="AF82" s="8" t="inlineStr"/>
-      <c r="AG82" s="9" t="inlineStr">
-        <is>
-          <t>VADN001</t>
-        </is>
-      </c>
+      <c r="AG82" s="9" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -9835,114 +10011,110 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>VADN026</t>
+          <t>VADN052</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="E83" s="9" t="inlineStr"/>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="inlineStr">
+        <is>
+          <t>VADN051</t>
+        </is>
+      </c>
       <c r="F83" s="9" t="inlineStr"/>
-      <c r="G83" s="8" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
-      <c r="H83" s="7" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="7" t="inlineStr"/>
       <c r="I83" s="8" t="inlineStr">
         <is>
-          <t>VADN002</t>
+          <t>VADN025</t>
         </is>
       </c>
       <c r="J83" s="8" t="inlineStr">
         <is>
-          <t>VADN022</t>
+          <t>VADN152</t>
         </is>
       </c>
       <c r="K83" s="8" t="inlineStr">
         <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="L83" s="9" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="M83" s="9" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="N83" s="8" t="inlineStr"/>
+      <c r="O83" s="8" t="inlineStr"/>
+      <c r="P83" s="8" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="Q83" s="8" t="inlineStr"/>
+      <c r="R83" s="8" t="inlineStr">
+        <is>
           <t>VADN005</t>
         </is>
       </c>
-      <c r="L83" s="9" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="M83" s="9" t="inlineStr"/>
-      <c r="N83" s="8" t="inlineStr"/>
-      <c r="O83" s="8" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="P83" s="8" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="Q83" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="R83" s="8" t="inlineStr">
+      <c r="S83" s="9" t="inlineStr">
         <is>
           <t>VADN029</t>
         </is>
       </c>
-      <c r="S83" s="9" t="inlineStr"/>
       <c r="T83" s="9" t="inlineStr"/>
       <c r="U83" s="8" t="inlineStr">
         <is>
-          <t>VADN025</t>
+          <t>VADN005</t>
         </is>
       </c>
       <c r="V83" s="8" t="inlineStr">
         <is>
-          <t>VADN034</t>
+          <t>VADN003</t>
         </is>
       </c>
       <c r="W83" s="8" t="inlineStr">
         <is>
-          <t>VADN052</t>
+          <t>VADN022</t>
         </is>
       </c>
       <c r="X83" s="8" t="inlineStr"/>
       <c r="Y83" s="8" t="inlineStr"/>
       <c r="Z83" s="9" t="inlineStr">
         <is>
-          <t>VADN002</t>
+          <t>VADN051</t>
         </is>
       </c>
       <c r="AA83" s="9" t="inlineStr"/>
-      <c r="AB83" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
+      <c r="AB83" s="8" t="inlineStr"/>
       <c r="AC83" s="8" t="inlineStr">
         <is>
-          <t>VADN005</t>
+          <t>VADN040</t>
         </is>
       </c>
       <c r="AD83" s="8" t="inlineStr">
         <is>
-          <t>VADN022</t>
+          <t>VADN028</t>
         </is>
       </c>
       <c r="AE83" s="8" t="inlineStr">
         <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="AF83" s="8" t="inlineStr"/>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="AF83" s="8" t="inlineStr">
+        <is>
+          <t>VADN040</t>
+        </is>
+      </c>
       <c r="AG83" s="9" t="inlineStr"/>
     </row>
     <row r="84">
@@ -9958,100 +10130,100 @@
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>VADN052</t>
+          <t>VADN029</t>
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr"/>
       <c r="E84" s="9" t="inlineStr"/>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>VADN029</t>
+          <t>VADN022</t>
         </is>
       </c>
       <c r="G84" s="8" t="inlineStr">
         <is>
-          <t>VADN030</t>
+          <t>VADN034</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>VADN027</t>
-        </is>
-      </c>
-      <c r="I84" s="8" t="inlineStr"/>
-      <c r="J84" s="8" t="inlineStr">
-        <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="K84" s="8" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
-      <c r="L84" s="9" t="inlineStr"/>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="J84" s="8" t="inlineStr"/>
+      <c r="K84" s="8" t="inlineStr"/>
+      <c r="L84" s="9" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
       <c r="M84" s="9" t="inlineStr"/>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>VADN030</t>
+          <t>VADN022</t>
         </is>
       </c>
       <c r="O84" s="8" t="inlineStr">
         <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="P84" s="8" t="inlineStr"/>
+      <c r="Q84" s="8" t="inlineStr"/>
+      <c r="R84" s="8" t="inlineStr">
+        <is>
+          <t>VADN004</t>
+        </is>
+      </c>
+      <c r="S84" s="9" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="T84" s="9" t="inlineStr"/>
+      <c r="U84" s="8" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="V84" s="8" t="inlineStr">
+        <is>
           <t>VADN051</t>
         </is>
       </c>
-      <c r="P84" s="8" t="inlineStr"/>
-      <c r="Q84" s="8" t="inlineStr">
+      <c r="W84" s="8" t="inlineStr"/>
+      <c r="X84" s="8" t="inlineStr">
+        <is>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="Y84" s="8" t="inlineStr"/>
+      <c r="Z84" s="9" t="inlineStr"/>
+      <c r="AA84" s="9" t="inlineStr"/>
+      <c r="AB84" s="8" t="inlineStr"/>
+      <c r="AC84" s="8" t="inlineStr">
         <is>
           <t>VADN025</t>
         </is>
       </c>
-      <c r="R84" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
-      <c r="S84" s="9" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
-      <c r="T84" s="9" t="inlineStr"/>
-      <c r="U84" s="8" t="inlineStr"/>
-      <c r="V84" s="8" t="inlineStr"/>
-      <c r="W84" s="8" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="X84" s="8" t="inlineStr"/>
-      <c r="Y84" s="8" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="Z84" s="9" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="AA84" s="9" t="inlineStr"/>
-      <c r="AB84" s="8" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="AC84" s="8" t="inlineStr"/>
-      <c r="AD84" s="8" t="inlineStr"/>
+      <c r="AD84" s="8" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
       <c r="AE84" s="8" t="inlineStr">
         <is>
-          <t>VADN003</t>
+          <t>VADN152</t>
         </is>
       </c>
       <c r="AF84" s="8" t="inlineStr">
         <is>
-          <t>VADN006</t>
+          <t>VADN001</t>
         </is>
       </c>
       <c r="AG84" s="9" t="inlineStr"/>
@@ -10069,111 +10241,107 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>VADN025</t>
+          <t>VADN006</t>
         </is>
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="inlineStr"/>
       <c r="F85" s="9" t="inlineStr"/>
-      <c r="G85" s="8" t="inlineStr"/>
+      <c r="G85" s="8" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>VADN051</t>
+          <t>VADN029</t>
         </is>
       </c>
       <c r="I85" s="8" t="inlineStr"/>
       <c r="J85" s="8" t="inlineStr"/>
       <c r="K85" s="8" t="inlineStr">
         <is>
-          <t>VADN002</t>
+          <t>VADN004</t>
         </is>
       </c>
       <c r="L85" s="9" t="inlineStr">
         <is>
-          <t>VADN026</t>
+          <t>VADN022</t>
         </is>
       </c>
       <c r="M85" s="9" t="inlineStr">
         <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="N85" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="N85" s="8" t="inlineStr"/>
       <c r="O85" s="8" t="inlineStr">
         <is>
-          <t>VADN030</t>
+          <t>VADN025</t>
         </is>
       </c>
       <c r="P85" s="8" t="inlineStr"/>
-      <c r="Q85" s="8" t="inlineStr"/>
+      <c r="Q85" s="8" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
       <c r="R85" s="8" t="inlineStr">
         <is>
-          <t>VADN004</t>
-        </is>
-      </c>
-      <c r="S85" s="9" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="S85" s="9" t="inlineStr"/>
       <c r="T85" s="9" t="inlineStr"/>
       <c r="U85" s="8" t="inlineStr">
         <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="V85" s="8" t="inlineStr"/>
+      <c r="W85" s="8" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="X85" s="8" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="Y85" s="8" t="inlineStr"/>
+      <c r="Z85" s="9" t="inlineStr"/>
+      <c r="AA85" s="9" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="AB85" s="8" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="AC85" s="8" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="AD85" s="8" t="inlineStr">
+        <is>
           <t>VADN029</t>
         </is>
       </c>
-      <c r="V85" s="8" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="W85" s="8" t="inlineStr"/>
-      <c r="X85" s="8" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="Y85" s="8" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
-      <c r="Z85" s="9" t="inlineStr"/>
-      <c r="AA85" s="9" t="inlineStr"/>
-      <c r="AB85" s="8" t="inlineStr"/>
-      <c r="AC85" s="8" t="inlineStr"/>
-      <c r="AD85" s="8" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="AE85" s="8" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
+      <c r="AE85" s="8" t="inlineStr"/>
       <c r="AF85" s="8" t="inlineStr">
         <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="AG85" s="9" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="AG85" s="9" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -10188,80 +10356,76 @@
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="E86" s="9" t="inlineStr"/>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="D86" s="8" t="inlineStr"/>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
       <c r="F86" s="9" t="inlineStr"/>
       <c r="G86" s="8" t="inlineStr">
         <is>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="H86" s="7" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="I86" s="8" t="inlineStr"/>
+      <c r="J86" s="8" t="inlineStr">
+        <is>
           <t>VADN022</t>
         </is>
       </c>
-      <c r="H86" s="7" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>VADN004</t>
-        </is>
-      </c>
-      <c r="J86" s="8" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
       <c r="K86" s="8" t="inlineStr">
         <is>
-          <t>VADN032</t>
+          <t>VADN005</t>
         </is>
       </c>
       <c r="L86" s="9" t="inlineStr"/>
       <c r="M86" s="9" t="inlineStr"/>
       <c r="N86" s="8" t="inlineStr">
         <is>
-          <t>VADN006</t>
+          <t>VADN025</t>
         </is>
       </c>
       <c r="O86" s="8" t="inlineStr">
         <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="P86" s="8" t="inlineStr">
+        <is>
           <t>VADN003</t>
         </is>
       </c>
-      <c r="P86" s="8" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
       <c r="Q86" s="8" t="inlineStr">
         <is>
-          <t>VADN028</t>
+          <t>VADN032</t>
         </is>
       </c>
       <c r="R86" s="8" t="inlineStr"/>
       <c r="S86" s="9" t="inlineStr"/>
-      <c r="T86" s="9" t="inlineStr"/>
-      <c r="U86" s="8" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
+      <c r="T86" s="9" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="U86" s="8" t="inlineStr"/>
       <c r="V86" s="8" t="inlineStr"/>
       <c r="W86" s="8" t="inlineStr">
         <is>
-          <t>VADN003</t>
+          <t>VADN002</t>
         </is>
       </c>
       <c r="X86" s="8" t="inlineStr">
         <is>
-          <t>VADN051</t>
+          <t>VADN025</t>
         </is>
       </c>
       <c r="Y86" s="8" t="inlineStr">
@@ -10270,25 +10434,33 @@
         </is>
       </c>
       <c r="Z86" s="9" t="inlineStr"/>
-      <c r="AA86" s="9" t="inlineStr"/>
+      <c r="AA86" s="9" t="inlineStr">
+        <is>
+          <t>VADN040</t>
+        </is>
+      </c>
       <c r="AB86" s="8" t="inlineStr"/>
-      <c r="AC86" s="8" t="inlineStr"/>
+      <c r="AC86" s="8" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
       <c r="AD86" s="8" t="inlineStr">
         <is>
-          <t>VADN034</t>
-        </is>
-      </c>
-      <c r="AE86" s="8" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="AE86" s="8" t="inlineStr"/>
       <c r="AF86" s="8" t="inlineStr">
         <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="AG86" s="9" t="inlineStr"/>
+          <t>VADN004</t>
+        </is>
+      </c>
+      <c r="AG86" s="9" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -10301,113 +10473,109 @@
           <t>PAT_VAL</t>
         </is>
       </c>
-      <c r="C87" s="7" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr"/>
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>VADN022</t>
         </is>
       </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="E87" s="9" t="inlineStr"/>
-      <c r="F87" s="9" t="inlineStr"/>
-      <c r="G87" s="8" t="inlineStr">
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="7" t="inlineStr"/>
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="L87" s="9" t="inlineStr"/>
+      <c r="M87" s="9" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="N87" s="8" t="inlineStr"/>
+      <c r="O87" s="8" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="P87" s="8" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="Q87" s="8" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="R87" s="8" t="inlineStr"/>
+      <c r="S87" s="9" t="inlineStr"/>
+      <c r="T87" s="9" t="inlineStr">
+        <is>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="U87" s="8" t="inlineStr"/>
+      <c r="V87" s="8" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="W87" s="8" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="X87" s="8" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="Y87" s="8" t="inlineStr"/>
+      <c r="Z87" s="9" t="inlineStr"/>
+      <c r="AA87" s="9" t="inlineStr">
         <is>
           <t>VADN029</t>
         </is>
       </c>
-      <c r="H87" s="7" t="inlineStr">
-        <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="J87" s="8" t="inlineStr"/>
-      <c r="K87" s="8" t="inlineStr"/>
-      <c r="L87" s="9" t="inlineStr">
-        <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="M87" s="9" t="inlineStr">
+      <c r="AB87" s="8" t="inlineStr"/>
+      <c r="AC87" s="8" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="AD87" s="8" t="inlineStr"/>
+      <c r="AE87" s="8" t="inlineStr">
         <is>
           <t>VADN025</t>
         </is>
       </c>
-      <c r="N87" s="8" t="inlineStr">
-        <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="O87" s="8" t="inlineStr"/>
-      <c r="P87" s="8" t="inlineStr"/>
-      <c r="Q87" s="8" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="R87" s="8" t="inlineStr"/>
-      <c r="S87" s="9" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="T87" s="9" t="inlineStr"/>
-      <c r="U87" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="V87" s="8" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="W87" s="8" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="X87" s="8" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
-      <c r="Y87" s="8" t="inlineStr"/>
-      <c r="Z87" s="9" t="inlineStr">
-        <is>
-          <t>VADN027</t>
-        </is>
-      </c>
-      <c r="AA87" s="9" t="inlineStr"/>
-      <c r="AB87" s="8" t="inlineStr"/>
-      <c r="AC87" s="8" t="inlineStr"/>
-      <c r="AD87" s="8" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="AE87" s="8" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
       <c r="AF87" s="8" t="inlineStr">
         <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="AG87" s="9" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="AG87" s="9" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -10420,109 +10588,113 @@
           <t>PAT_VAL</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr"/>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
       <c r="D88" s="8" t="inlineStr"/>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>VADN026</t>
-        </is>
-      </c>
-      <c r="F88" s="9" t="inlineStr"/>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>VADN029</t>
+        </is>
+      </c>
       <c r="G88" s="8" t="inlineStr">
         <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="H88" s="7" t="inlineStr">
+        <is>
           <t>VADN032</t>
         </is>
       </c>
-      <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>VADN029</t>
+        </is>
+      </c>
       <c r="J88" s="8" t="inlineStr">
         <is>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="K88" s="8" t="inlineStr"/>
+      <c r="L88" s="9" t="inlineStr"/>
+      <c r="M88" s="9" t="inlineStr"/>
+      <c r="N88" s="8" t="inlineStr">
+        <is>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="O88" s="8" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="P88" s="8" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="Q88" s="8" t="inlineStr"/>
+      <c r="R88" s="8" t="inlineStr"/>
+      <c r="S88" s="9" t="inlineStr"/>
+      <c r="T88" s="9" t="inlineStr">
+        <is>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="U88" s="8" t="inlineStr"/>
+      <c r="V88" s="8" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="W88" s="8" t="inlineStr">
+        <is>
+          <t>VADN031</t>
+        </is>
+      </c>
+      <c r="X88" s="8" t="inlineStr">
+        <is>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="Y88" s="8" t="inlineStr"/>
+      <c r="Z88" s="9" t="inlineStr"/>
+      <c r="AA88" s="9" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="AB88" s="8" t="inlineStr"/>
+      <c r="AC88" s="8" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="AD88" s="8" t="inlineStr">
+        <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="AE88" s="8" t="inlineStr"/>
+      <c r="AF88" s="8" t="inlineStr">
+        <is>
           <t>VADN002</t>
         </is>
       </c>
-      <c r="K88" s="8" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
-      <c r="L88" s="9" t="inlineStr">
-        <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="M88" s="9" t="inlineStr">
-        <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="N88" s="8" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="O88" s="8" t="inlineStr"/>
-      <c r="P88" s="8" t="inlineStr"/>
-      <c r="Q88" s="8" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="R88" s="8" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="S88" s="9" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="T88" s="9" t="inlineStr"/>
-      <c r="U88" s="8" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="V88" s="8" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="W88" s="8" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="X88" s="8" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
-      <c r="Y88" s="8" t="inlineStr">
-        <is>
-          <t>VADN004</t>
-        </is>
-      </c>
-      <c r="Z88" s="9" t="inlineStr"/>
-      <c r="AA88" s="9" t="inlineStr"/>
-      <c r="AB88" s="8" t="inlineStr"/>
-      <c r="AC88" s="8" t="inlineStr"/>
-      <c r="AD88" s="8" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="AE88" s="8" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
-      <c r="AF88" s="8" t="inlineStr">
-        <is>
-          <t>VADN051</t>
-        </is>
-      </c>
-      <c r="AG88" s="9" t="inlineStr"/>
+      <c r="AG88" s="9" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
@@ -10535,113 +10707,113 @@
           <t>PAT_VAL</t>
         </is>
       </c>
-      <c r="C89" s="7" t="inlineStr"/>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
       <c r="D89" s="8" t="inlineStr"/>
       <c r="E89" s="9" t="inlineStr">
         <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="F89" s="9" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr"/>
       <c r="G89" s="8" t="inlineStr">
         <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr"/>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="H89" s="7" t="inlineStr">
+        <is>
+          <t>VADN027</t>
+        </is>
+      </c>
       <c r="I89" s="8" t="inlineStr">
         <is>
-          <t>VADN001</t>
+          <t>VADN030</t>
         </is>
       </c>
       <c r="J89" s="8" t="inlineStr">
         <is>
-          <t>VADN003</t>
+          <t>VADN032</t>
         </is>
       </c>
       <c r="K89" s="8" t="inlineStr">
         <is>
-          <t>VADN028</t>
+          <t>VADN030</t>
         </is>
       </c>
       <c r="L89" s="9" t="inlineStr"/>
       <c r="M89" s="9" t="inlineStr"/>
       <c r="N89" s="8" t="inlineStr">
         <is>
-          <t>VADN002</t>
+          <t>VADN004</t>
         </is>
       </c>
       <c r="O89" s="8" t="inlineStr">
         <is>
-          <t>VADN032</t>
+          <t>VADN028</t>
         </is>
       </c>
       <c r="P89" s="8" t="inlineStr">
         <is>
-          <t>VADN032</t>
-        </is>
-      </c>
-      <c r="Q89" s="8" t="inlineStr"/>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="Q89" s="8" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
       <c r="R89" s="8" t="inlineStr"/>
-      <c r="S89" s="9" t="inlineStr">
-        <is>
-          <t>VADN034</t>
-        </is>
-      </c>
+      <c r="S89" s="9" t="inlineStr"/>
       <c r="T89" s="9" t="inlineStr">
         <is>
-          <t>VADN051</t>
+          <t>VADN028</t>
         </is>
       </c>
       <c r="U89" s="8" t="inlineStr"/>
       <c r="V89" s="8" t="inlineStr">
         <is>
-          <t>VADN006</t>
+          <t>VADN004</t>
         </is>
       </c>
       <c r="W89" s="8" t="inlineStr">
         <is>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="X89" s="8" t="inlineStr"/>
+      <c r="Y89" s="8" t="inlineStr"/>
+      <c r="Z89" s="9" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="AA89" s="9" t="inlineStr">
+        <is>
           <t>VADN025</t>
         </is>
       </c>
-      <c r="X89" s="8" t="inlineStr"/>
-      <c r="Y89" s="8" t="inlineStr">
-        <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="Z89" s="9" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="AA89" s="9" t="inlineStr"/>
-      <c r="AB89" s="8" t="inlineStr"/>
-      <c r="AC89" s="8" t="inlineStr"/>
+      <c r="AB89" s="8" t="inlineStr">
+        <is>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="AC89" s="8" t="inlineStr">
+        <is>
+          <t>VADN051</t>
+        </is>
+      </c>
       <c r="AD89" s="8" t="inlineStr">
         <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="AE89" s="8" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
-      <c r="AF89" s="8" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="AG89" s="9" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="AE89" s="8" t="inlineStr"/>
+      <c r="AF89" s="8" t="inlineStr"/>
+      <c r="AG89" s="9" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -10654,88 +10826,84 @@
           <t>PAT_VAL</t>
         </is>
       </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="D90" s="8" t="inlineStr"/>
-      <c r="E90" s="9" t="inlineStr"/>
+      <c r="C90" s="7" t="inlineStr"/>
+      <c r="D90" s="8" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="E90" s="9" t="inlineStr">
+        <is>
+          <t>VADN029</t>
+        </is>
+      </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
+          <t>VADN028</t>
+        </is>
+      </c>
+      <c r="G90" s="8" t="inlineStr"/>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
           <t>VADN005</t>
         </is>
       </c>
-      <c r="G90" s="8" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="H90" s="7" t="inlineStr">
-        <is>
-          <t>VADN052</t>
-        </is>
-      </c>
-      <c r="I90" s="8" t="inlineStr"/>
-      <c r="J90" s="8" t="inlineStr"/>
-      <c r="K90" s="8" t="inlineStr">
-        <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="L90" s="9" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="J90" s="8" t="inlineStr">
+        <is>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="K90" s="8" t="inlineStr"/>
+      <c r="L90" s="9" t="inlineStr"/>
       <c r="M90" s="9" t="inlineStr">
         <is>
+          <t>VADN040</t>
+        </is>
+      </c>
+      <c r="N90" s="8" t="inlineStr">
+        <is>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
+      <c r="P90" s="8" t="inlineStr">
+        <is>
           <t>VADN028</t>
         </is>
       </c>
-      <c r="N90" s="8" t="inlineStr"/>
-      <c r="O90" s="8" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="P90" s="8" t="inlineStr">
-        <is>
-          <t>VADN031</t>
-        </is>
-      </c>
       <c r="Q90" s="8" t="inlineStr">
         <is>
-          <t>VADN034</t>
-        </is>
-      </c>
-      <c r="R90" s="8" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="R90" s="8" t="inlineStr"/>
       <c r="S90" s="9" t="inlineStr"/>
-      <c r="T90" s="9" t="inlineStr"/>
+      <c r="T90" s="9" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
       <c r="U90" s="8" t="inlineStr">
         <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="V90" s="8" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="V90" s="8" t="inlineStr"/>
       <c r="W90" s="8" t="inlineStr">
         <is>
-          <t>VADN002</t>
-        </is>
-      </c>
-      <c r="X90" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="X90" s="8" t="inlineStr"/>
       <c r="Y90" s="8" t="inlineStr">
         <is>
           <t>VADN051</t>
@@ -10745,26 +10913,26 @@
       <c r="AA90" s="9" t="inlineStr"/>
       <c r="AB90" s="8" t="inlineStr">
         <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="AC90" s="8" t="inlineStr">
-        <is>
-          <t>VADN030</t>
-        </is>
-      </c>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="AC90" s="8" t="inlineStr"/>
       <c r="AD90" s="8" t="inlineStr">
         <is>
-          <t>VADN030</t>
+          <t>VADN052</t>
         </is>
       </c>
       <c r="AE90" s="8" t="inlineStr">
         <is>
-          <t>VADN031</t>
+          <t>VADN051</t>
         </is>
       </c>
       <c r="AF90" s="8" t="inlineStr"/>
-      <c r="AG90" s="9" t="inlineStr"/>
+      <c r="AG90" s="9" t="inlineStr">
+        <is>
+          <t>VADN034</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -10779,21 +10947,21 @@
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>VADN038</t>
+          <t>VADN032</t>
         </is>
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr"/>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>VADN028</t>
+        </is>
+      </c>
       <c r="F91" s="9" t="inlineStr"/>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
+      <c r="G91" s="8" t="inlineStr"/>
       <c r="H91" s="7" t="inlineStr">
         <is>
           <t>VADN022</t>
@@ -10801,87 +10969,91 @@
       </c>
       <c r="I91" s="8" t="inlineStr">
         <is>
-          <t>VADN029</t>
+          <t>VADN022</t>
         </is>
       </c>
       <c r="J91" s="8" t="inlineStr"/>
       <c r="K91" s="8" t="inlineStr"/>
       <c r="L91" s="9" t="inlineStr">
         <is>
-          <t>VADN006</t>
+          <t>VADN005</t>
         </is>
       </c>
       <c r="M91" s="9" t="inlineStr">
         <is>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="N91" s="8" t="inlineStr">
+        <is>
           <t>VADN052</t>
         </is>
       </c>
-      <c r="N91" s="8" t="inlineStr"/>
       <c r="O91" s="8" t="inlineStr">
         <is>
-          <t>VADN004</t>
+          <t>VADN051</t>
         </is>
       </c>
       <c r="P91" s="8" t="inlineStr"/>
       <c r="Q91" s="8" t="inlineStr"/>
       <c r="R91" s="8" t="inlineStr">
         <is>
-          <t>VADN152</t>
+          <t>VADN022</t>
         </is>
       </c>
       <c r="S91" s="9" t="inlineStr">
         <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="T91" s="9" t="inlineStr">
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="T91" s="9" t="inlineStr"/>
+      <c r="U91" s="8" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="V91" s="8" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="W91" s="8" t="inlineStr">
+        <is>
+          <t>VADN005</t>
+        </is>
+      </c>
+      <c r="X91" s="8" t="inlineStr">
         <is>
           <t>VADN028</t>
         </is>
       </c>
-      <c r="U91" s="8" t="inlineStr"/>
-      <c r="V91" s="8" t="inlineStr"/>
-      <c r="W91" s="8" t="inlineStr">
-        <is>
-          <t>VADN004</t>
-        </is>
-      </c>
-      <c r="X91" s="8" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
       <c r="Y91" s="8" t="inlineStr">
         <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="Z91" s="9" t="inlineStr">
-        <is>
-          <t>VADN038</t>
-        </is>
-      </c>
+          <t>VADN030</t>
+        </is>
+      </c>
+      <c r="Z91" s="9" t="inlineStr"/>
       <c r="AA91" s="9" t="inlineStr"/>
       <c r="AB91" s="8" t="inlineStr">
         <is>
-          <t>VADN006</t>
+          <t>VADN002</t>
         </is>
       </c>
       <c r="AC91" s="8" t="inlineStr">
         <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="AD91" s="8" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
-      <c r="AE91" s="8" t="inlineStr"/>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="AD91" s="8" t="inlineStr"/>
+      <c r="AE91" s="8" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
       <c r="AF91" s="8" t="inlineStr"/>
       <c r="AG91" s="9" t="inlineStr">
         <is>
-          <t>VADN005</t>
+          <t>VADN022</t>
         </is>
       </c>
     </row>
@@ -10898,103 +11070,107 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="D92" s="8" t="inlineStr">
+        <is>
+          <t>VADN001</t>
+        </is>
+      </c>
+      <c r="E92" s="9" t="inlineStr"/>
+      <c r="F92" s="9" t="inlineStr"/>
+      <c r="G92" s="8" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
           <t>VADN051</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr"/>
-      <c r="E92" s="9" t="inlineStr"/>
-      <c r="F92" s="9" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="G92" s="8" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="8" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
+      <c r="I92" s="8" t="inlineStr"/>
       <c r="J92" s="8" t="inlineStr">
         <is>
-          <t>VADN040</t>
-        </is>
-      </c>
-      <c r="K92" s="8" t="inlineStr"/>
+          <t>VADN052</t>
+        </is>
+      </c>
+      <c r="K92" s="8" t="inlineStr">
+        <is>
+          <t>VADN051</t>
+        </is>
+      </c>
       <c r="L92" s="9" t="inlineStr"/>
       <c r="M92" s="9" t="inlineStr"/>
       <c r="N92" s="8" t="inlineStr">
         <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="O92" s="8" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
+          <t>VADN051</t>
+        </is>
+      </c>
+      <c r="O92" s="8" t="inlineStr"/>
       <c r="P92" s="8" t="inlineStr">
         <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="Q92" s="8" t="inlineStr"/>
-      <c r="R92" s="8" t="inlineStr">
-        <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="S92" s="9" t="inlineStr">
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="Q92" s="8" t="inlineStr">
+        <is>
+          <t>VADN029</t>
+        </is>
+      </c>
+      <c r="R92" s="8" t="inlineStr"/>
+      <c r="S92" s="9" t="inlineStr"/>
+      <c r="T92" s="9" t="inlineStr">
         <is>
           <t>VADN051</t>
         </is>
       </c>
-      <c r="T92" s="9" t="inlineStr"/>
       <c r="U92" s="8" t="inlineStr"/>
-      <c r="V92" s="8" t="inlineStr"/>
-      <c r="W92" s="8" t="inlineStr">
+      <c r="V92" s="8" t="inlineStr">
         <is>
           <t>VADN029</t>
         </is>
       </c>
-      <c r="X92" s="8" t="inlineStr">
-        <is>
-          <t>VADN028</t>
-        </is>
-      </c>
+      <c r="W92" s="8" t="inlineStr"/>
+      <c r="X92" s="8" t="inlineStr"/>
       <c r="Y92" s="8" t="inlineStr">
         <is>
-          <t>VADN029</t>
-        </is>
-      </c>
-      <c r="Z92" s="9" t="inlineStr"/>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="Z92" s="9" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
       <c r="AA92" s="9" t="inlineStr">
         <is>
-          <t>VADN025</t>
+          <t>VADN005</t>
         </is>
       </c>
       <c r="AB92" s="8" t="inlineStr">
         <is>
-          <t>VADN030</t>
+          <t>VADN005</t>
         </is>
       </c>
       <c r="AC92" s="8" t="inlineStr">
         <is>
-          <t>VADN029</t>
+          <t>VADN032</t>
         </is>
       </c>
       <c r="AD92" s="8" t="inlineStr"/>
-      <c r="AE92" s="8" t="inlineStr"/>
-      <c r="AF92" s="8" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="AG92" s="9" t="inlineStr"/>
+      <c r="AE92" s="8" t="inlineStr">
+        <is>
+          <t>VADN032</t>
+        </is>
+      </c>
+      <c r="AF92" s="8" t="inlineStr"/>
+      <c r="AG92" s="9" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
@@ -11008,66 +11184,66 @@
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr"/>
-      <c r="D93" s="8" t="inlineStr"/>
-      <c r="E93" s="9" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
+      <c r="E93" s="9" t="inlineStr"/>
       <c r="F93" s="9" t="inlineStr"/>
       <c r="G93" s="8" t="inlineStr"/>
       <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="8" t="inlineStr"/>
-      <c r="J93" s="8" t="inlineStr">
+      <c r="I93" s="8" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
+      <c r="J93" s="8" t="inlineStr"/>
       <c r="K93" s="8" t="inlineStr"/>
-      <c r="L93" s="9" t="inlineStr"/>
-      <c r="M93" s="9" t="inlineStr">
+      <c r="L93" s="9" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
+      <c r="M93" s="9" t="inlineStr"/>
       <c r="N93" s="8" t="inlineStr"/>
-      <c r="O93" s="8" t="inlineStr"/>
-      <c r="P93" s="8" t="inlineStr">
+      <c r="O93" s="8" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
-      <c r="Q93" s="8" t="inlineStr"/>
+      <c r="P93" s="8" t="inlineStr"/>
+      <c r="Q93" s="8" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="R93" s="8" t="inlineStr"/>
-      <c r="S93" s="9" t="inlineStr">
+      <c r="S93" s="9" t="inlineStr"/>
+      <c r="T93" s="9" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
-      <c r="T93" s="9" t="inlineStr"/>
       <c r="U93" s="8" t="inlineStr"/>
       <c r="V93" s="8" t="inlineStr"/>
       <c r="W93" s="8" t="inlineStr">
         <is>
-          <t>VADU47127</t>
+          <t>VADP003</t>
         </is>
       </c>
       <c r="X93" s="8" t="inlineStr"/>
       <c r="Y93" s="8" t="inlineStr"/>
-      <c r="Z93" s="9" t="inlineStr"/>
+      <c r="Z93" s="9" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="AA93" s="9" t="inlineStr"/>
       <c r="AB93" s="8" t="inlineStr"/>
-      <c r="AC93" s="8" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
+      <c r="AC93" s="8" t="inlineStr"/>
       <c r="AD93" s="8" t="inlineStr"/>
-      <c r="AE93" s="8" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
+      <c r="AE93" s="8" t="inlineStr"/>
       <c r="AF93" s="8" t="inlineStr"/>
       <c r="AG93" s="9" t="inlineStr"/>
     </row>
@@ -11086,65 +11262,61 @@
       <c r="D94" s="8" t="inlineStr"/>
       <c r="E94" s="9" t="inlineStr"/>
       <c r="F94" s="9" t="inlineStr"/>
-      <c r="G94" s="8" t="inlineStr"/>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
+      <c r="G94" s="8" t="inlineStr">
+        <is>
+          <t>VADP003</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr"/>
       <c r="I94" s="8" t="inlineStr"/>
-      <c r="J94" s="8" t="inlineStr"/>
+      <c r="J94" s="8" t="inlineStr">
+        <is>
+          <t>VADP003</t>
+        </is>
+      </c>
       <c r="K94" s="8" t="inlineStr"/>
       <c r="L94" s="9" t="inlineStr"/>
-      <c r="M94" s="9" t="inlineStr"/>
+      <c r="M94" s="9" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="N94" s="8" t="inlineStr"/>
-      <c r="O94" s="8" t="inlineStr"/>
+      <c r="O94" s="8" t="inlineStr">
+        <is>
+          <t>VADP003</t>
+        </is>
+      </c>
       <c r="P94" s="8" t="inlineStr"/>
-      <c r="Q94" s="8" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
+      <c r="Q94" s="8" t="inlineStr"/>
       <c r="R94" s="8" t="inlineStr"/>
       <c r="S94" s="9" t="inlineStr"/>
-      <c r="T94" s="9" t="inlineStr">
+      <c r="T94" s="9" t="inlineStr"/>
+      <c r="U94" s="8" t="inlineStr"/>
+      <c r="V94" s="8" t="inlineStr"/>
+      <c r="W94" s="8" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
-      <c r="U94" s="8" t="inlineStr"/>
-      <c r="V94" s="8" t="inlineStr">
+      <c r="X94" s="8" t="inlineStr"/>
+      <c r="Y94" s="8" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
-      <c r="W94" s="8" t="inlineStr"/>
-      <c r="X94" s="8" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
-      <c r="Y94" s="8" t="inlineStr"/>
       <c r="Z94" s="9" t="inlineStr"/>
       <c r="AA94" s="9" t="inlineStr"/>
-      <c r="AB94" s="8" t="inlineStr">
+      <c r="AB94" s="8" t="inlineStr"/>
+      <c r="AC94" s="8" t="inlineStr"/>
+      <c r="AD94" s="8" t="inlineStr"/>
+      <c r="AE94" s="8" t="inlineStr"/>
+      <c r="AF94" s="8" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
-      <c r="AC94" s="8" t="inlineStr"/>
-      <c r="AD94" s="8" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
-      <c r="AE94" s="8" t="inlineStr"/>
-      <c r="AF94" s="8" t="inlineStr"/>
-      <c r="AG94" s="9" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
+      <c r="AG94" s="9" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
@@ -11159,35 +11331,31 @@
       </c>
       <c r="C95" s="7" t="inlineStr"/>
       <c r="D95" s="8" t="inlineStr"/>
-      <c r="E95" s="9" t="inlineStr"/>
-      <c r="F95" s="9" t="inlineStr">
+      <c r="E95" s="9" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
+      <c r="F95" s="9" t="inlineStr"/>
       <c r="G95" s="8" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>VADP003</t>
-        </is>
-      </c>
+      <c r="H95" s="7" t="inlineStr"/>
       <c r="I95" s="8" t="inlineStr"/>
       <c r="J95" s="8" t="inlineStr"/>
-      <c r="K95" s="8" t="inlineStr"/>
+      <c r="K95" s="8" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="L95" s="9" t="inlineStr"/>
       <c r="M95" s="9" t="inlineStr"/>
-      <c r="N95" s="8" t="inlineStr"/>
-      <c r="O95" s="8" t="inlineStr">
+      <c r="N95" s="8" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
+      <c r="O95" s="8" t="inlineStr"/>
       <c r="P95" s="8" t="inlineStr"/>
-      <c r="Q95" s="8" t="inlineStr">
-        <is>
-          <t>VADP003</t>
-        </is>
-      </c>
+      <c r="Q95" s="8" t="inlineStr"/>
       <c r="R95" s="8" t="inlineStr"/>
       <c r="S95" s="9" t="inlineStr"/>
       <c r="T95" s="9" t="inlineStr"/>
@@ -11197,21 +11365,29 @@
       <c r="X95" s="8" t="inlineStr"/>
       <c r="Y95" s="8" t="inlineStr">
         <is>
-          <t>VADU47127</t>
+          <t>VADP003</t>
         </is>
       </c>
       <c r="Z95" s="9" t="inlineStr"/>
       <c r="AA95" s="9" t="inlineStr"/>
-      <c r="AB95" s="8" t="inlineStr"/>
+      <c r="AB95" s="8" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="AC95" s="8" t="inlineStr"/>
-      <c r="AD95" s="8" t="inlineStr"/>
+      <c r="AD95" s="8" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="AE95" s="8" t="inlineStr"/>
-      <c r="AF95" s="8" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
-      <c r="AG95" s="9" t="inlineStr"/>
+      <c r="AF95" s="8" t="inlineStr"/>
+      <c r="AG95" s="9" t="inlineStr">
+        <is>
+          <t>VADP003</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -11241,17 +11417,13 @@
       <c r="I96" s="8" t="inlineStr"/>
       <c r="J96" s="8" t="inlineStr"/>
       <c r="K96" s="8" t="inlineStr"/>
-      <c r="L96" s="9" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
+      <c r="L96" s="9" t="inlineStr"/>
       <c r="M96" s="9" t="inlineStr"/>
       <c r="N96" s="8" t="inlineStr"/>
       <c r="O96" s="8" t="inlineStr"/>
       <c r="P96" s="8" t="inlineStr">
         <is>
-          <t>VADP003</t>
+          <t>VADU47127</t>
         </is>
       </c>
       <c r="Q96" s="8" t="inlineStr"/>
@@ -11263,15 +11435,19 @@
       <c r="S96" s="9" t="inlineStr"/>
       <c r="T96" s="9" t="inlineStr"/>
       <c r="U96" s="8" t="inlineStr"/>
-      <c r="V96" s="8" t="inlineStr">
+      <c r="V96" s="8" t="inlineStr"/>
+      <c r="W96" s="8" t="inlineStr"/>
+      <c r="X96" s="8" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
-      <c r="W96" s="8" t="inlineStr"/>
-      <c r="X96" s="8" t="inlineStr"/>
       <c r="Y96" s="8" t="inlineStr"/>
-      <c r="Z96" s="9" t="inlineStr"/>
+      <c r="Z96" s="9" t="inlineStr">
+        <is>
+          <t>VADP003</t>
+        </is>
+      </c>
       <c r="AA96" s="9" t="inlineStr"/>
       <c r="AB96" s="8" t="inlineStr">
         <is>
@@ -11280,12 +11456,12 @@
       </c>
       <c r="AC96" s="8" t="inlineStr"/>
       <c r="AD96" s="8" t="inlineStr"/>
-      <c r="AE96" s="8" t="inlineStr"/>
-      <c r="AF96" s="8" t="inlineStr">
+      <c r="AE96" s="8" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
+      <c r="AF96" s="8" t="inlineStr"/>
       <c r="AG96" s="9" t="inlineStr"/>
     </row>
     <row r="97">
@@ -11299,59 +11475,59 @@
           <t>PAT_VAL_24H</t>
         </is>
       </c>
-      <c r="C97" s="7" t="inlineStr"/>
+      <c r="C97" s="7" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="D97" s="8" t="inlineStr"/>
       <c r="E97" s="9" t="inlineStr"/>
       <c r="F97" s="9" t="inlineStr"/>
-      <c r="G97" s="8" t="inlineStr">
-        <is>
-          <t>VADP003</t>
-        </is>
-      </c>
-      <c r="H97" s="7" t="inlineStr"/>
-      <c r="I97" s="8" t="inlineStr">
-        <is>
-          <t>VADP003</t>
-        </is>
-      </c>
-      <c r="J97" s="8" t="inlineStr"/>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="7" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
+      <c r="I97" s="8" t="inlineStr"/>
+      <c r="J97" s="8" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="K97" s="8" t="inlineStr"/>
       <c r="L97" s="9" t="inlineStr"/>
-      <c r="M97" s="9" t="inlineStr">
+      <c r="M97" s="9" t="inlineStr"/>
+      <c r="N97" s="8" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
-      <c r="N97" s="8" t="inlineStr"/>
       <c r="O97" s="8" t="inlineStr"/>
       <c r="P97" s="8" t="inlineStr"/>
       <c r="Q97" s="8" t="inlineStr"/>
       <c r="R97" s="8" t="inlineStr"/>
-      <c r="S97" s="9" t="inlineStr">
+      <c r="S97" s="9" t="inlineStr"/>
+      <c r="T97" s="9" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
-      <c r="T97" s="9" t="inlineStr"/>
-      <c r="U97" s="8" t="inlineStr">
+      <c r="U97" s="8" t="inlineStr"/>
+      <c r="V97" s="8" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
-      <c r="V97" s="8" t="inlineStr"/>
       <c r="W97" s="8" t="inlineStr"/>
-      <c r="X97" s="8" t="inlineStr">
-        <is>
-          <t>VADP003</t>
-        </is>
-      </c>
+      <c r="X97" s="8" t="inlineStr"/>
       <c r="Y97" s="8" t="inlineStr"/>
-      <c r="Z97" s="9" t="inlineStr">
-        <is>
-          <t>VADP003</t>
-        </is>
-      </c>
-      <c r="AA97" s="9" t="inlineStr"/>
+      <c r="Z97" s="9" t="inlineStr"/>
+      <c r="AA97" s="9" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="AB97" s="8" t="inlineStr"/>
       <c r="AC97" s="8" t="inlineStr"/>
       <c r="AD97" s="8" t="inlineStr">
@@ -11374,63 +11550,63 @@
           <t>PAT_VAL_24H</t>
         </is>
       </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr"/>
+      <c r="D98" s="8" t="inlineStr"/>
+      <c r="E98" s="9" t="inlineStr"/>
+      <c r="F98" s="9" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
-      <c r="D98" s="8" t="inlineStr"/>
-      <c r="E98" s="9" t="inlineStr">
+      <c r="G98" s="8" t="inlineStr"/>
+      <c r="H98" s="7" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
-      <c r="F98" s="9" t="inlineStr"/>
-      <c r="G98" s="8" t="inlineStr"/>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="8" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
+      <c r="I98" s="8" t="inlineStr"/>
       <c r="J98" s="8" t="inlineStr"/>
-      <c r="K98" s="8" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
+      <c r="K98" s="8" t="inlineStr"/>
       <c r="L98" s="9" t="inlineStr"/>
       <c r="M98" s="9" t="inlineStr"/>
       <c r="N98" s="8" t="inlineStr"/>
-      <c r="O98" s="8" t="inlineStr">
-        <is>
-          <t>VADP003</t>
-        </is>
-      </c>
+      <c r="O98" s="8" t="inlineStr"/>
       <c r="P98" s="8" t="inlineStr"/>
       <c r="Q98" s="8" t="inlineStr"/>
-      <c r="R98" s="8" t="inlineStr"/>
+      <c r="R98" s="8" t="inlineStr">
+        <is>
+          <t>VADP003</t>
+        </is>
+      </c>
       <c r="S98" s="9" t="inlineStr"/>
       <c r="T98" s="9" t="inlineStr"/>
-      <c r="U98" s="8" t="inlineStr">
+      <c r="U98" s="8" t="inlineStr"/>
+      <c r="V98" s="8" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
-      <c r="V98" s="8" t="inlineStr"/>
       <c r="W98" s="8" t="inlineStr"/>
-      <c r="X98" s="8" t="inlineStr"/>
+      <c r="X98" s="8" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="Y98" s="8" t="inlineStr"/>
       <c r="Z98" s="9" t="inlineStr"/>
-      <c r="AA98" s="9" t="inlineStr">
+      <c r="AA98" s="9" t="inlineStr"/>
+      <c r="AB98" s="8" t="inlineStr"/>
+      <c r="AC98" s="8" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
-      <c r="AB98" s="8" t="inlineStr"/>
-      <c r="AC98" s="8" t="inlineStr"/>
       <c r="AD98" s="8" t="inlineStr"/>
-      <c r="AE98" s="8" t="inlineStr"/>
+      <c r="AE98" s="8" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="AF98" s="8" t="inlineStr"/>
       <c r="AG98" s="9" t="inlineStr"/>
     </row>
@@ -11446,56 +11622,52 @@
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr"/>
-      <c r="D99" s="8" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr"/>
+      <c r="E99" s="9" t="inlineStr"/>
+      <c r="F99" s="9" t="inlineStr">
         <is>
           <t>VADU47127</t>
         </is>
       </c>
-      <c r="E99" s="9" t="inlineStr"/>
-      <c r="F99" s="9" t="inlineStr"/>
       <c r="G99" s="8" t="inlineStr"/>
       <c r="H99" s="7" t="inlineStr"/>
       <c r="I99" s="8" t="inlineStr"/>
-      <c r="J99" s="8" t="inlineStr">
+      <c r="J99" s="8" t="inlineStr"/>
+      <c r="K99" s="8" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
-      <c r="K99" s="8" t="inlineStr"/>
-      <c r="L99" s="9" t="inlineStr">
+      <c r="L99" s="9" t="inlineStr"/>
+      <c r="M99" s="9" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
-      <c r="M99" s="9" t="inlineStr"/>
-      <c r="N99" s="8" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
+      <c r="N99" s="8" t="inlineStr"/>
       <c r="O99" s="8" t="inlineStr"/>
       <c r="P99" s="8" t="inlineStr"/>
-      <c r="Q99" s="8" t="inlineStr"/>
-      <c r="R99" s="8" t="inlineStr">
+      <c r="Q99" s="8" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
-      <c r="S99" s="9" t="inlineStr"/>
+      <c r="R99" s="8" t="inlineStr"/>
+      <c r="S99" s="9" t="inlineStr">
+        <is>
+          <t>VADP003</t>
+        </is>
+      </c>
       <c r="T99" s="9" t="inlineStr"/>
-      <c r="U99" s="8" t="inlineStr"/>
+      <c r="U99" s="8" t="inlineStr">
+        <is>
+          <t>VADP003</t>
+        </is>
+      </c>
       <c r="V99" s="8" t="inlineStr"/>
-      <c r="W99" s="8" t="inlineStr">
-        <is>
-          <t>VADP003</t>
-        </is>
-      </c>
+      <c r="W99" s="8" t="inlineStr"/>
       <c r="X99" s="8" t="inlineStr"/>
-      <c r="Y99" s="8" t="inlineStr">
-        <is>
-          <t>VADP003</t>
-        </is>
-      </c>
+      <c r="Y99" s="8" t="inlineStr"/>
       <c r="Z99" s="9" t="inlineStr"/>
       <c r="AA99" s="9" t="inlineStr"/>
       <c r="AB99" s="8" t="inlineStr"/>
@@ -11522,43 +11694,47 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>VADU47127</t>
+          <t>VADP003</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr"/>
       <c r="E100" s="9" t="inlineStr"/>
-      <c r="F100" s="9" t="inlineStr">
-        <is>
-          <t>VADU47127</t>
-        </is>
-      </c>
+      <c r="F100" s="9" t="inlineStr"/>
       <c r="G100" s="8" t="inlineStr"/>
       <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="8" t="inlineStr"/>
+      <c r="I100" s="8" t="inlineStr">
+        <is>
+          <t>VADP003</t>
+        </is>
+      </c>
       <c r="J100" s="8" t="inlineStr"/>
-      <c r="K100" s="8" t="inlineStr">
+      <c r="K100" s="8" t="inlineStr"/>
+      <c r="L100" s="9" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
-      <c r="L100" s="9" t="inlineStr"/>
       <c r="M100" s="9" t="inlineStr"/>
-      <c r="N100" s="8" t="inlineStr">
+      <c r="N100" s="8" t="inlineStr"/>
+      <c r="O100" s="8" t="inlineStr"/>
+      <c r="P100" s="8" t="inlineStr">
         <is>
           <t>VADP003</t>
         </is>
       </c>
-      <c r="O100" s="8" t="inlineStr"/>
-      <c r="P100" s="8" t="inlineStr"/>
       <c r="Q100" s="8" t="inlineStr"/>
       <c r="R100" s="8" t="inlineStr"/>
-      <c r="S100" s="9" t="inlineStr"/>
-      <c r="T100" s="9" t="inlineStr">
-        <is>
-          <t>VADP003</t>
-        </is>
-      </c>
-      <c r="U100" s="8" t="inlineStr"/>
+      <c r="S100" s="9" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
+      <c r="T100" s="9" t="inlineStr"/>
+      <c r="U100" s="8" t="inlineStr">
+        <is>
+          <t>VADU47127</t>
+        </is>
+      </c>
       <c r="V100" s="8" t="inlineStr"/>
       <c r="W100" s="8" t="inlineStr"/>
       <c r="X100" s="8" t="inlineStr"/>
@@ -11572,15 +11748,11 @@
       <c r="AB100" s="8" t="inlineStr"/>
       <c r="AC100" s="8" t="inlineStr"/>
       <c r="AD100" s="8" t="inlineStr"/>
-      <c r="AE100" s="8" t="inlineStr">
-        <is>
-          <t>VADP003</t>
-        </is>
-      </c>
+      <c r="AE100" s="8" t="inlineStr"/>
       <c r="AF100" s="8" t="inlineStr"/>
       <c r="AG100" s="9" t="inlineStr">
         <is>
-          <t>VADP003</t>
+          <t>VADU47127</t>
         </is>
       </c>
     </row>
@@ -11594,151 +11766,161 @@
     <row r="103">
       <c r="G103" s="11" t="inlineStr">
         <is>
+          <t>VADN004</t>
+        </is>
+      </c>
+      <c r="H103" s="11" t="inlineStr">
+        <is>
           <t>VADN003</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>VADN024</t>
+          <t>VADN035</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr">
         <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="K103" s="11" t="inlineStr">
+        <is>
+          <t>VADN035</t>
+        </is>
+      </c>
+      <c r="N103" s="11" t="inlineStr">
+        <is>
+          <t>VADN035</t>
+        </is>
+      </c>
+      <c r="O103" s="11" t="inlineStr">
+        <is>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="P103" s="11" t="inlineStr">
+        <is>
           <t>VADN007</t>
         </is>
       </c>
-      <c r="K103" s="11" t="inlineStr">
+      <c r="Q103" s="11" t="inlineStr">
         <is>
           <t>VADN007</t>
         </is>
       </c>
-      <c r="N103" s="11" t="inlineStr">
-        <is>
-          <t>VADN035</t>
-        </is>
-      </c>
-      <c r="O103" s="11" t="inlineStr">
+      <c r="R103" s="11" t="inlineStr">
+        <is>
+          <t>VADN007</t>
+        </is>
+      </c>
+      <c r="S103" s="11" t="inlineStr">
         <is>
           <t>VADN001</t>
         </is>
       </c>
-      <c r="P103" s="11" t="inlineStr">
-        <is>
-          <t>VADN007</t>
-        </is>
-      </c>
-      <c r="Q103" s="11" t="inlineStr">
-        <is>
-          <t>VADN007</t>
-        </is>
-      </c>
-      <c r="R103" s="11" t="inlineStr">
-        <is>
-          <t>VADN007</t>
-        </is>
-      </c>
-      <c r="S103" s="11" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
       <c r="U103" s="11" t="inlineStr">
         <is>
-          <t>VADN004</t>
+          <t>VADN002</t>
         </is>
       </c>
       <c r="V103" s="11" t="inlineStr">
         <is>
-          <t>VADN022</t>
+          <t>VADN001</t>
         </is>
       </c>
       <c r="W103" s="11" t="inlineStr">
         <is>
-          <t>VADN024</t>
+          <t>VADN008</t>
         </is>
       </c>
       <c r="X103" s="11" t="inlineStr">
         <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="Y103" s="11" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="Z103" s="11" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
+      <c r="AB103" s="11" t="inlineStr">
+        <is>
+          <t>VADN023</t>
+        </is>
+      </c>
+      <c r="AC103" s="11" t="inlineStr">
+        <is>
           <t>VADN036</t>
         </is>
       </c>
-      <c r="Y103" s="11" t="inlineStr">
+      <c r="AD103" s="11" t="inlineStr">
+        <is>
+          <t>VADN008</t>
+        </is>
+      </c>
+      <c r="AE103" s="11" t="inlineStr">
         <is>
           <t>VADN036</t>
         </is>
       </c>
-      <c r="Z103" s="11" t="inlineStr">
-        <is>
-          <t>VADN022</t>
-        </is>
-      </c>
-      <c r="AB103" s="11" t="inlineStr">
-        <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="AC103" s="11" t="inlineStr">
-        <is>
-          <t>VADN001</t>
-        </is>
-      </c>
-      <c r="AD103" s="11" t="inlineStr">
-        <is>
-          <t>VADN008</t>
-        </is>
-      </c>
-      <c r="AE103" s="11" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
       <c r="AF103" s="11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>VADN036</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="G104" s="11" t="inlineStr">
         <is>
-          <t>VADN004</t>
+          <t>VADN006</t>
+        </is>
+      </c>
+      <c r="H104" s="11" t="inlineStr">
+        <is>
+          <t>VADN006</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
+          <t>VADN171</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr">
+        <is>
           <t>VADN025</t>
         </is>
       </c>
-      <c r="J104" s="11" t="inlineStr">
+      <c r="O104" s="11" t="inlineStr">
         <is>
           <t>VADN035</t>
         </is>
       </c>
-      <c r="K104" s="11" t="inlineStr">
+      <c r="P104" s="11" t="inlineStr">
+        <is>
+          <t>VADN012</t>
+        </is>
+      </c>
+      <c r="Q104" s="11" t="inlineStr">
         <is>
           <t>VADN035</t>
         </is>
       </c>
-      <c r="O104" s="11" t="inlineStr">
-        <is>
-          <t>VADN005</t>
-        </is>
-      </c>
-      <c r="P104" s="11" t="inlineStr">
-        <is>
-          <t>VADN035</t>
-        </is>
-      </c>
-      <c r="Q104" s="11" t="inlineStr">
-        <is>
-          <t>VADN035</t>
-        </is>
-      </c>
       <c r="R104" s="11" t="inlineStr">
         <is>
           <t>VADN012</t>
         </is>
       </c>
+      <c r="S104" s="11" t="inlineStr">
+        <is>
+          <t>VADN002</t>
+        </is>
+      </c>
       <c r="U104" s="11" t="inlineStr">
         <is>
           <t>VADN007</t>
@@ -11746,37 +11928,37 @@
       </c>
       <c r="V104" s="11" t="inlineStr">
         <is>
+          <t>VADN022</t>
+        </is>
+      </c>
+      <c r="W104" s="11" t="inlineStr">
+        <is>
           <t>VADN036</t>
         </is>
       </c>
-      <c r="W104" s="11" t="inlineStr">
+      <c r="X104" s="11" t="inlineStr">
+        <is>
+          <t>VADN008</t>
+        </is>
+      </c>
+      <c r="Y104" s="11" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="Z104" s="11" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
+      <c r="AB104" s="11" t="inlineStr">
         <is>
           <t>VADN036</t>
         </is>
       </c>
-      <c r="AB104" s="11" t="inlineStr">
-        <is>
-          <t>VADN003</t>
-        </is>
-      </c>
-      <c r="AC104" s="11" t="inlineStr">
-        <is>
-          <t>VADN002</t>
-        </is>
-      </c>
       <c r="AD104" s="11" t="inlineStr">
         <is>
-          <t>VADN013</t>
-        </is>
-      </c>
-      <c r="AE104" s="11" t="inlineStr">
-        <is>
-          <t>VADN008</t>
-        </is>
-      </c>
-      <c r="AF104" s="11" t="inlineStr">
-        <is>
-          <t>REF CAL M</t>
+          <t>VADN036</t>
         </is>
       </c>
     </row>
@@ -11786,13 +11968,18 @@
           <t>VADN035</t>
         </is>
       </c>
-      <c r="I105" s="11" t="inlineStr">
+      <c r="J105" s="11" t="inlineStr">
         <is>
           <t>VADN035</t>
         </is>
       </c>
       <c r="O105" s="11" t="inlineStr">
         <is>
+          <t>VADN176</t>
+        </is>
+      </c>
+      <c r="P105" s="11" t="inlineStr">
+        <is>
           <t>VADN035</t>
         </is>
       </c>
@@ -11801,51 +11988,51 @@
           <t>VADN035</t>
         </is>
       </c>
+      <c r="S105" s="11" t="inlineStr">
+        <is>
+          <t>VADN003</t>
+        </is>
+      </c>
       <c r="U105" s="11" t="inlineStr">
         <is>
+          <t>VADN012</t>
+        </is>
+      </c>
+      <c r="V105" s="11" t="inlineStr">
+        <is>
+          <t>VADN036</t>
+        </is>
+      </c>
+      <c r="W105" s="11" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
+      <c r="X105" s="11" t="inlineStr">
+        <is>
+          <t>VADN036</t>
+        </is>
+      </c>
+      <c r="Y105" s="11" t="inlineStr">
+        <is>
           <t>VADN008</t>
         </is>
       </c>
-      <c r="V105" s="11" t="inlineStr">
+      <c r="Z105" s="11" t="inlineStr">
+        <is>
+          <t>VADN025</t>
+        </is>
+      </c>
+      <c r="AB105" s="11" t="inlineStr">
         <is>
           <t>VADN172</t>
-        </is>
-      </c>
-      <c r="W105" s="11" t="inlineStr">
-        <is>
-          <t>VADN172</t>
-        </is>
-      </c>
-      <c r="AB105" s="11" t="inlineStr">
-        <is>
-          <t>VADN004</t>
-        </is>
-      </c>
-      <c r="AC105" s="11" t="inlineStr">
-        <is>
-          <t>VADN004</t>
-        </is>
-      </c>
-      <c r="AD105" s="11" t="inlineStr">
-        <is>
-          <t>VADN036</t>
-        </is>
-      </c>
-      <c r="AE105" s="11" t="inlineStr">
-        <is>
-          <t>VADN013</t>
-        </is>
-      </c>
-      <c r="AF105" s="11" t="inlineStr">
-        <is>
-          <t>VADN004</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="O106" s="11" t="inlineStr">
-        <is>
-          <t>VADN176</t>
+      <c r="S106" s="11" t="inlineStr">
+        <is>
+          <t>VADN022</t>
         </is>
       </c>
       <c r="U106" s="11" t="inlineStr">
@@ -11853,73 +12040,48 @@
           <t>VADN013</t>
         </is>
       </c>
-      <c r="AB106" s="11" t="inlineStr">
-        <is>
-          <t>VADN008</t>
-        </is>
-      </c>
-      <c r="AC106" s="11" t="inlineStr">
-        <is>
-          <t>VADN006</t>
-        </is>
-      </c>
-      <c r="AE106" s="11" t="inlineStr">
+      <c r="X106" s="11" t="inlineStr">
+        <is>
+          <t>VADN172</t>
+        </is>
+      </c>
+      <c r="Y106" s="11" t="inlineStr">
         <is>
           <t>VADN036</t>
         </is>
       </c>
-      <c r="AF106" s="11" t="inlineStr">
-        <is>
-          <t>VADN007</t>
+      <c r="Z106" s="11" t="inlineStr">
+        <is>
+          <t>VADN027</t>
         </is>
       </c>
     </row>
     <row r="107">
+      <c r="S107" s="11" t="inlineStr">
+        <is>
+          <t>VADN027</t>
+        </is>
+      </c>
       <c r="U107" s="11" t="inlineStr">
         <is>
           <t>VADN023</t>
         </is>
       </c>
-      <c r="AB107" s="11" t="inlineStr">
-        <is>
-          <t>VADN009</t>
-        </is>
-      </c>
-      <c r="AC107" s="11" t="inlineStr">
-        <is>
-          <t>VADN008</t>
-        </is>
-      </c>
-      <c r="AE107" s="11" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="AF107" s="11" t="inlineStr">
-        <is>
-          <t>VADN008</t>
+      <c r="Y107" s="11" t="inlineStr">
+        <is>
+          <t>VADN172</t>
         </is>
       </c>
     </row>
     <row r="108">
+      <c r="S108" s="11" t="inlineStr">
+        <is>
+          <t>VADN152</t>
+        </is>
+      </c>
       <c r="U108" s="11" t="inlineStr">
         <is>
           <t>VADN035</t>
-        </is>
-      </c>
-      <c r="AB108" s="11" t="inlineStr">
-        <is>
-          <t>VADN011</t>
-        </is>
-      </c>
-      <c r="AC108" s="11" t="inlineStr">
-        <is>
-          <t>VADN009</t>
-        </is>
-      </c>
-      <c r="AF108" s="11" t="inlineStr">
-        <is>
-          <t>VADN010</t>
         </is>
       </c>
     </row>
@@ -11929,21 +12091,6 @@
           <t>VADN036</t>
         </is>
       </c>
-      <c r="AB109" s="11" t="inlineStr">
-        <is>
-          <t>VADN013</t>
-        </is>
-      </c>
-      <c r="AC109" s="11" t="inlineStr">
-        <is>
-          <t>VADN011</t>
-        </is>
-      </c>
-      <c r="AF109" s="11" t="inlineStr">
-        <is>
-          <t>VADN012</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="U110" s="11" t="inlineStr">
@@ -11951,255 +12098,11 @@
           <t>VADN171</t>
         </is>
       </c>
-      <c r="AB110" s="11" t="inlineStr">
-        <is>
-          <t>VADN023</t>
-        </is>
-      </c>
-      <c r="AC110" s="11" t="inlineStr">
-        <is>
-          <t>VADN013</t>
-        </is>
-      </c>
-      <c r="AF110" s="11" t="inlineStr">
-        <is>
-          <t>VADN013</t>
-        </is>
-      </c>
     </row>
     <row r="111">
-      <c r="AB111" s="11" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="AC111" s="11" t="inlineStr">
-        <is>
-          <t>VADN023</t>
-        </is>
-      </c>
-      <c r="AF111" s="11" t="inlineStr">
-        <is>
-          <t>VADN014</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="AB112" s="11" t="inlineStr">
-        <is>
-          <t>VADN036</t>
-        </is>
-      </c>
-      <c r="AC112" s="11" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-      <c r="AF112" s="11" t="inlineStr">
-        <is>
-          <t>VADN015</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="AB113" s="11" t="inlineStr">
-        <is>
-          <t>VADN172</t>
-        </is>
-      </c>
-      <c r="AC113" s="11" t="inlineStr">
-        <is>
-          <t>VADN036</t>
-        </is>
-      </c>
-      <c r="AF113" s="11" t="inlineStr">
-        <is>
-          <t>VADN016</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="AC114" s="11" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-      <c r="AF114" s="11" t="inlineStr">
-        <is>
-          <t>VADN017</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="AC115" s="11" t="inlineStr">
-        <is>
-          <t>VADN172</t>
-        </is>
-      </c>
-      <c r="AF115" s="11" t="inlineStr">
-        <is>
-          <t>VADN018</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="AF116" s="11" t="inlineStr">
-        <is>
-          <t>VADN019</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="AF117" s="11" t="inlineStr">
-        <is>
-          <t>VADN020</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="AF118" s="11" t="inlineStr">
-        <is>
-          <t>VADN021</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="AF119" s="11" t="inlineStr">
-        <is>
-          <t>VADN025</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="AF120" s="11" t="inlineStr">
-        <is>
-          <t>VADN036</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="AF121" s="11" t="inlineStr">
-        <is>
-          <t>VADN037</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="AF122" s="11" t="inlineStr">
-        <is>
-          <t>VADN151</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="AF123" s="11" t="inlineStr">
-        <is>
-          <t>VADN152</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="AF124" s="11" t="inlineStr">
-        <is>
-          <t>VADN161</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="AF125" s="11" t="inlineStr">
-        <is>
-          <t>VADN164</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="AF126" s="11" t="inlineStr">
-        <is>
-          <t>VADN171</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="AF127" s="11" t="inlineStr">
-        <is>
-          <t>VADN172</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="AF128" s="11" t="inlineStr">
-        <is>
-          <t>VADN174</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="AF129" s="11" t="inlineStr">
-        <is>
-          <t>VADN175</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="AF130" s="11" t="inlineStr">
+      <c r="U111" s="11" t="inlineStr">
         <is>
           <t>VADN176</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="AF131" s="11" t="inlineStr">
-        <is>
-          <t>VADN179</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="AF132" s="11" t="inlineStr">
-        <is>
-          <t>VADN182</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="AF133" s="11" t="inlineStr">
-        <is>
-          <t>VADN191</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="AF134" s="11" t="inlineStr">
-        <is>
-          <t>VADN192</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="AF135" s="11" t="inlineStr">
-        <is>
-          <t>VADN193</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="AF136" s="11" t="inlineStr">
-        <is>
-          <t>VADN195</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="AF137" s="11" t="inlineStr">
-        <is>
-          <t>VADP001</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="AF138" s="11" t="inlineStr">
-        <is>
-          <t>VADP002</t>
         </is>
       </c>
     </row>
